--- a/ModExcel/J技能buff配置表.xlsx
+++ b/ModExcel/J技能buff配置表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\SurvivorsData\trunk\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9AFC05A-6608-415E-B7F2-823B2C5A7938}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D4B5537-4DDD-4684-8A17-30CA279228C9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -176,7 +176,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3185" uniqueCount="2056">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3185" uniqueCount="2057">
   <si>
     <t>F:\workspace_linux\xgame\server\trunk_vbox\scripts\data\xml\buff.xml</t>
   </si>
@@ -6339,9 +6339,6 @@
     <t>buff死亡引爆</t>
   </si>
   <si>
-    <t>die_cast_buff(1,2,10000)</t>
-  </si>
-  <si>
     <t>buff组id，释放技能id，几率</t>
   </si>
   <si>
@@ -7191,10 +7188,6 @@
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
-    <t>cast_spell(54014)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
     <t>skill_hit_trigger_buff(50011,1,10000,0)</t>
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
@@ -8132,6 +8125,18 @@
   </si>
   <si>
     <t>change_attri(301,1)</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>healing(-5)</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>die_cast_buff(1,2,10000)</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>107,109</t>
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
 </sst>
@@ -9185,6 +9190,312 @@
     <cellStyle name="常规 3" xfId="4" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
   </cellStyles>
   <dxfs count="192">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -10845,312 +11156,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="微软雅黑"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="微软雅黑"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="微软雅黑"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="微软雅黑"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="微软雅黑"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="微软雅黑"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="微软雅黑"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="微软雅黑"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="微软雅黑"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="微软雅黑"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="微软雅黑"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="微软雅黑"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="微软雅黑"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="微软雅黑"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="微软雅黑"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="微软雅黑"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="微软雅黑"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -12124,82 +12129,82 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="表1" displayName="表1" ref="D5:AC601" tableType="xml" totalsRowShown="0" connectionId="43">
   <autoFilter ref="D5:AC601" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="26">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" uniqueName="id_i" name="id_i" dataDxfId="191">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" uniqueName="id_i" name="id_i" dataDxfId="25">
       <xmlColumnPr mapId="77" xpath="/root/buff/id_i" xmlDataType="double"/>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" uniqueName="name_i" name="name_i" dataDxfId="190">
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" uniqueName="name_i" name="name_i" dataDxfId="24">
       <xmlColumnPr mapId="77" xpath="/root/buff/name_i" xmlDataType="double"/>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" uniqueName="desc_i" name="desc_i" dataDxfId="189">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" uniqueName="desc_i" name="desc_i" dataDxfId="23">
       <xmlColumnPr mapId="77" xpath="/root/buff/desc_i" xmlDataType="double"/>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" uniqueName="icon_i" name="icon_i" dataDxfId="188">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" uniqueName="icon_i" name="icon_i" dataDxfId="22">
       <xmlColumnPr mapId="77" xpath="/root/buff/icon_i" xmlDataType="double"/>
     </tableColumn>
-    <tableColumn id="62" xr3:uid="{00000000-0010-0000-0000-00003E000000}" uniqueName="isshow_i" name="isshow_i" dataDxfId="187">
+    <tableColumn id="62" xr3:uid="{00000000-0010-0000-0000-00003E000000}" uniqueName="isshow_i" name="isshow_i" dataDxfId="21">
       <xmlColumnPr mapId="77" xpath="/root/buff/isshow_i" xmlDataType="double"/>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" uniqueName="total_time_i" name="total_time_i" dataDxfId="186">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" uniqueName="total_time_i" name="total_time_i" dataDxfId="20">
       <xmlColumnPr mapId="77" xpath="/root/buff/total_time_i" xmlDataType="double"/>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" uniqueName="delay_time_i" name="delay_time_i" dataDxfId="185">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" uniqueName="delay_time_i" name="delay_time_i" dataDxfId="19">
       <xmlColumnPr mapId="77" xpath="/root/buff/delay_time_i" xmlDataType="double"/>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" uniqueName="replace_type_i" name="replace_type_i" dataDxfId="184">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" uniqueName="replace_type_i" name="replace_type_i" dataDxfId="18">
       <xmlColumnPr mapId="77" xpath="/root/buff/replace_type_i" xmlDataType="double"/>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" uniqueName="buff_layer_i" name="buff_layer_i" dataDxfId="183">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" uniqueName="buff_layer_i" name="buff_layer_i" dataDxfId="17">
       <xmlColumnPr mapId="77" xpath="/root/buff/buff_layer_i" xmlDataType="double"/>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" uniqueName="buff_type_i" name="buff_type_i" dataDxfId="182">
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" uniqueName="buff_type_i" name="buff_type_i" dataDxfId="16">
       <xmlColumnPr mapId="77" xpath="/root/buff/buff_type_i" xmlDataType="double"/>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" uniqueName="BuffShutDownType_i" name="BuffShutDownType_i" dataDxfId="181">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" uniqueName="BuffShutDownType_i" name="BuffShutDownType_i" dataDxfId="15">
       <xmlColumnPr mapId="77" xpath="/root/buff/BuffShutDownType_i" xmlDataType="double"/>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" uniqueName="group_i" name="group_i" dataDxfId="180">
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" uniqueName="group_i" name="group_i" dataDxfId="14">
       <xmlColumnPr mapId="77" xpath="/root/buff/group_i" xmlDataType="double"/>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" uniqueName="group_level_i" name="group_level_i" dataDxfId="179">
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" uniqueName="group_level_i" name="group_level_i" dataDxfId="13">
       <xmlColumnPr mapId="77" xpath="/root/buff/group_level_i" xmlDataType="double"/>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" uniqueName="exclude_buffs_group_l" name="exclude_buffs_group_l" dataDxfId="178">
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" uniqueName="exclude_buffs_group_l" name="exclude_buffs_group_l" dataDxfId="12">
       <xmlColumnPr mapId="77" xpath="/root/buff/exclude_buffs_group_l" xmlDataType="double"/>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" uniqueName="replace_buffs_group_l" name="replace_buffs_group_l" dataDxfId="177">
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" uniqueName="replace_buffs_group_l" name="replace_buffs_group_l" dataDxfId="11">
       <xmlColumnPr mapId="77" xpath="/root/buff/replace_buffs_group_l" xmlDataType="double"/>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" uniqueName="exclude_buffs_l" name="exclude_buffs_l" dataDxfId="176">
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" uniqueName="exclude_buffs_l" name="exclude_buffs_l" dataDxfId="10">
       <xmlColumnPr mapId="77" xpath="/root/buff/exclude_buffs_l" xmlDataType="double"/>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" uniqueName="exexclude_buffs_l" name="exexclude_buffs_l" dataDxfId="175">
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" uniqueName="exexclude_buffs_l" name="exexclude_buffs_l" dataDxfId="9">
       <xmlColumnPr mapId="77" xpath="/root/buff/exexclude_buffs_l" xmlDataType="double"/>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" uniqueName="replace_buffs_l" name="replace_buffs_l" dataDxfId="174">
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" uniqueName="replace_buffs_l" name="replace_buffs_l" dataDxfId="8">
       <xmlColumnPr mapId="77" xpath="/root/buff/replace_buffs_l" xmlDataType="double"/>
     </tableColumn>
-    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" uniqueName="start_effect_s" name="start_effect_s" dataDxfId="173">
+    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" uniqueName="start_effect_s" name="start_effect_s" dataDxfId="7">
       <xmlColumnPr mapId="77" xpath="/root/buff/start_effect_s" xmlDataType="double"/>
     </tableColumn>
-    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0000-000021000000}" uniqueName="end_effect_s" name="end_effect_s" dataDxfId="172">
+    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0000-000021000000}" uniqueName="end_effect_s" name="end_effect_s" dataDxfId="6">
       <xmlColumnPr mapId="77" xpath="/root/buff/end_effect_s" xmlDataType="double"/>
     </tableColumn>
-    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" uniqueName="update_effect_s" name="update_effect_s" dataDxfId="171">
+    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" uniqueName="update_effect_s" name="update_effect_s" dataDxfId="5">
       <xmlColumnPr mapId="77" xpath="/root/buff/update_effect_s" xmlDataType="double"/>
     </tableColumn>
-    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0000-000023000000}" uniqueName="time_effect_s" name="time_effect_s" dataDxfId="170">
+    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0000-000023000000}" uniqueName="time_effect_s" name="time_effect_s" dataDxfId="4">
       <xmlColumnPr mapId="77" xpath="/root/buff/time_effect_s" xmlDataType="double"/>
     </tableColumn>
-    <tableColumn id="42" xr3:uid="{00000000-0010-0000-0000-00002A000000}" uniqueName="effect_events_s" name="effect_events_s" dataDxfId="169">
+    <tableColumn id="42" xr3:uid="{00000000-0010-0000-0000-00002A000000}" uniqueName="effect_events_s" name="effect_events_s" dataDxfId="3">
       <xmlColumnPr mapId="77" xpath="/root/buff/effect_events_s" xmlDataType="double"/>
     </tableColumn>
-    <tableColumn id="63" xr3:uid="{00000000-0010-0000-0000-00003F000000}" uniqueName="effectb_events_s" name="effectb_events_s" dataDxfId="168">
+    <tableColumn id="63" xr3:uid="{00000000-0010-0000-0000-00003F000000}" uniqueName="effectb_events_s" name="effectb_events_s" dataDxfId="2">
       <xmlColumnPr mapId="77" xpath="/root/buff/effectb_events_s" xmlDataType="double"/>
     </tableColumn>
-    <tableColumn id="64" xr3:uid="{00000000-0010-0000-0000-000040000000}" uniqueName="effectg_events_s" name="effectg_events_s" dataDxfId="167">
+    <tableColumn id="64" xr3:uid="{00000000-0010-0000-0000-000040000000}" uniqueName="effectg_events_s" name="effectg_events_s" dataDxfId="1">
       <xmlColumnPr mapId="77" xpath="/root/buff/effectg_events_s" xmlDataType="double"/>
     </tableColumn>
-    <tableColumn id="68" xr3:uid="{00000000-0010-0000-0000-000044000000}" uniqueName="buffend_effect_s" name="buffend_effect_s" dataDxfId="166">
+    <tableColumn id="68" xr3:uid="{00000000-0010-0000-0000-000044000000}" uniqueName="buffend_effect_s" name="buffend_effect_s" dataDxfId="0">
       <xmlColumnPr mapId="77" xpath="/root/buff/buffend_effect_s" xmlDataType="double"/>
     </tableColumn>
   </tableColumns>
@@ -12534,7 +12539,7 @@
         <v>1</v>
       </c>
       <c r="Q1" s="83" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="R1" s="109"/>
       <c r="S1"/>
@@ -12688,7 +12693,7 @@
         <v>36</v>
       </c>
       <c r="O4" s="129" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="P4" s="129" t="s">
         <v>37</v>
@@ -12735,13 +12740,13 @@
     </row>
     <row r="5" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="D5" s="83" t="s">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="E5" s="83" t="s">
         <v>1021</v>
       </c>
       <c r="F5" s="83" t="s">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="G5" s="83" t="s">
         <v>52</v>
@@ -12925,7 +12930,7 @@
       <c r="T7" s="137"/>
       <c r="U7" s="115"/>
       <c r="V7" s="115" t="s">
-        <v>2047</v>
+        <v>2045</v>
       </c>
       <c r="W7" s="115"/>
       <c r="X7" s="115"/>
@@ -12991,7 +12996,7 @@
       <c r="X8" s="115"/>
       <c r="Y8" s="115"/>
       <c r="Z8" s="115" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="AA8" s="115" t="s">
         <v>85</v>
@@ -13151,7 +13156,7 @@
         <v>83</v>
       </c>
       <c r="Q11" s="115" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="R11" s="115"/>
       <c r="S11" s="137" t="s">
@@ -13166,7 +13171,7 @@
       <c r="X11" s="115"/>
       <c r="Y11" s="115"/>
       <c r="Z11" s="115" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="AA11" s="115" t="s">
         <v>95</v>
@@ -13210,7 +13215,7 @@
       </c>
       <c r="P12" s="115"/>
       <c r="Q12" s="115" t="s">
-        <v>1851</v>
+        <v>1849</v>
       </c>
       <c r="R12" s="115"/>
       <c r="S12" s="137" t="s">
@@ -13273,7 +13278,7 @@
       </c>
       <c r="P13" s="115"/>
       <c r="Q13" s="115" t="s">
-        <v>1852</v>
+        <v>1850</v>
       </c>
       <c r="R13" s="115"/>
       <c r="S13" s="137" t="s">
@@ -13336,7 +13341,7 @@
       </c>
       <c r="P14" s="115"/>
       <c r="Q14" s="115" t="s">
-        <v>1853</v>
+        <v>1851</v>
       </c>
       <c r="R14" s="115"/>
       <c r="S14" s="137" t="s">
@@ -13353,7 +13358,7 @@
       <c r="X14" s="115"/>
       <c r="Y14" s="115"/>
       <c r="Z14" s="115" t="s">
-        <v>1883</v>
+        <v>1881</v>
       </c>
       <c r="AA14" s="115" t="s">
         <v>114</v>
@@ -13397,7 +13402,7 @@
       </c>
       <c r="P15" s="115"/>
       <c r="Q15" s="115" t="s">
-        <v>1853</v>
+        <v>1851</v>
       </c>
       <c r="R15" s="115"/>
       <c r="S15" s="137"/>
@@ -13448,7 +13453,7 @@
       </c>
       <c r="P16" s="115"/>
       <c r="Q16" s="115" t="s">
-        <v>1847</v>
+        <v>1845</v>
       </c>
       <c r="R16" s="115"/>
       <c r="S16" s="137"/>
@@ -13507,7 +13512,7 @@
       </c>
       <c r="P17" s="115"/>
       <c r="Q17" s="115" t="s">
-        <v>1847</v>
+        <v>1845</v>
       </c>
       <c r="R17" s="115"/>
       <c r="S17" s="137"/>
@@ -13566,14 +13571,14 @@
       </c>
       <c r="P18" s="115"/>
       <c r="Q18" s="115" t="s">
-        <v>1875</v>
+        <v>1873</v>
       </c>
       <c r="R18" s="115"/>
       <c r="S18" s="137"/>
       <c r="T18" s="137"/>
       <c r="U18" s="115"/>
       <c r="V18" s="115" t="s">
-        <v>1874</v>
+        <v>1872</v>
       </c>
       <c r="W18" s="115"/>
       <c r="X18" s="115"/>
@@ -13625,7 +13630,7 @@
       </c>
       <c r="P19" s="115"/>
       <c r="Q19" s="115" t="s">
-        <v>1847</v>
+        <v>1845</v>
       </c>
       <c r="R19" s="115"/>
       <c r="S19" s="137"/>
@@ -13986,7 +13991,7 @@
     </row>
     <row r="28" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="B28" s="118" t="s">
-        <v>1849</v>
+        <v>1847</v>
       </c>
       <c r="D28" s="83">
         <v>2007</v>
@@ -14060,7 +14065,7 @@
     </row>
     <row r="30" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="B30" s="118" t="s">
-        <v>1854</v>
+        <v>1852</v>
       </c>
       <c r="D30" s="83">
         <v>2009</v>
@@ -14078,7 +14083,7 @@
       <c r="M30" s="83"/>
       <c r="N30" s="115"/>
       <c r="O30" s="115" t="s">
-        <v>1848</v>
+        <v>1846</v>
       </c>
       <c r="P30" s="115"/>
       <c r="Q30" s="115"/>
@@ -14124,7 +14129,7 @@
       </c>
       <c r="P31" s="115"/>
       <c r="Q31" s="115" t="s">
-        <v>148</v>
+        <v>2056</v>
       </c>
       <c r="R31" s="115"/>
       <c r="S31" s="137"/>
@@ -14548,7 +14553,7 @@
         <v>174</v>
       </c>
       <c r="B42" s="162" t="s">
-        <v>1884</v>
+        <v>1882</v>
       </c>
       <c r="C42" s="163">
         <v>10002</v>
@@ -14719,7 +14724,7 @@
         <v>180</v>
       </c>
       <c r="B45" s="162" t="s">
-        <v>1872</v>
+        <v>1870</v>
       </c>
       <c r="C45" s="120"/>
       <c r="D45" s="83">
@@ -14745,13 +14750,13 @@
       <c r="T45" s="137"/>
       <c r="U45" s="115"/>
       <c r="V45" s="115" t="s">
-        <v>1871</v>
+        <v>1869</v>
       </c>
       <c r="W45" s="115"/>
       <c r="X45" s="115"/>
       <c r="Y45" s="115"/>
       <c r="Z45" s="115" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
       <c r="AA45" s="115" t="s">
         <v>183</v>
@@ -14764,7 +14769,7 @@
     <row r="46" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A46" s="163"/>
       <c r="B46" s="162" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="C46" s="120"/>
       <c r="D46" s="83">
@@ -14794,7 +14799,7 @@
       <c r="V46" s="115"/>
       <c r="W46" s="115"/>
       <c r="X46" s="115" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="Y46" s="115"/>
       <c r="Z46" s="115" t="s">
@@ -14813,7 +14818,7 @@
         <v>181</v>
       </c>
       <c r="B47" s="160" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="C47" s="161"/>
       <c r="D47" s="83">
@@ -14860,7 +14865,7 @@
         <v>184</v>
       </c>
       <c r="B48" s="160" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="C48" s="161"/>
       <c r="D48" s="83">
@@ -14900,10 +14905,10 @@
     </row>
     <row r="49" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A49" s="160" t="s">
+        <v>1754</v>
+      </c>
+      <c r="B49" s="160" t="s">
         <v>1755</v>
-      </c>
-      <c r="B49" s="160" t="s">
-        <v>1756</v>
       </c>
       <c r="C49" s="161"/>
       <c r="D49" s="83">
@@ -14939,7 +14944,7 @@
       <c r="V49" s="115"/>
       <c r="W49" s="115"/>
       <c r="X49" s="115" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="Y49" s="115"/>
       <c r="Z49" s="115" t="s">
@@ -14958,7 +14963,7 @@
         <v>186</v>
       </c>
       <c r="B50" s="160" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="C50" s="161"/>
       <c r="D50" s="83">
@@ -14999,7 +15004,7 @@
         <v>188</v>
       </c>
       <c r="B51" s="160" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="C51" s="161"/>
       <c r="D51" s="83">
@@ -15025,7 +15030,7 @@
       <c r="T51" s="137"/>
       <c r="U51" s="115"/>
       <c r="V51" s="115" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="W51" s="115"/>
       <c r="X51" s="115"/>
@@ -15040,7 +15045,7 @@
         <v>189</v>
       </c>
       <c r="B52" s="160" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="C52" s="161"/>
       <c r="D52" s="83">
@@ -15085,7 +15090,7 @@
         <v>191</v>
       </c>
       <c r="B53" s="160" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="C53" s="161"/>
       <c r="D53" s="83">
@@ -15130,7 +15135,7 @@
         <v>193</v>
       </c>
       <c r="B54" s="160" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="C54" s="161"/>
       <c r="D54" s="83">
@@ -15175,7 +15180,7 @@
         <v>195</v>
       </c>
       <c r="B55" s="160" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="C55" s="161"/>
       <c r="D55" s="83">
@@ -15220,7 +15225,7 @@
         <v>197</v>
       </c>
       <c r="B56" s="160" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="C56" s="161"/>
       <c r="D56" s="83">
@@ -15261,7 +15266,7 @@
         <v>199</v>
       </c>
       <c r="B57" s="160" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="C57" s="161"/>
       <c r="D57" s="83">
@@ -15299,10 +15304,10 @@
     </row>
     <row r="58" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A58" s="160" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="B58" s="160" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="C58" s="161"/>
       <c r="D58" s="83">
@@ -15332,7 +15337,7 @@
       <c r="T58" s="137"/>
       <c r="U58" s="115"/>
       <c r="V58" s="115" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
       <c r="W58" s="115"/>
       <c r="X58" s="115"/>
@@ -15344,10 +15349,10 @@
     </row>
     <row r="59" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A59" s="160" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="B59" s="160" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="C59" s="161"/>
       <c r="D59" s="83">
@@ -15377,7 +15382,7 @@
       <c r="T59" s="137"/>
       <c r="U59" s="115"/>
       <c r="V59" s="115" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="W59" s="115"/>
       <c r="X59" s="115"/>
@@ -15389,10 +15394,10 @@
     </row>
     <row r="60" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A60" s="160" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="B60" s="160" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="C60" s="161"/>
       <c r="D60" s="83">
@@ -15422,7 +15427,7 @@
       <c r="T60" s="137"/>
       <c r="U60" s="115"/>
       <c r="V60" s="115" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="W60" s="115"/>
       <c r="X60" s="115"/>
@@ -15434,10 +15439,10 @@
     </row>
     <row r="61" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A61" s="190" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="B61" s="160" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="C61" s="161"/>
       <c r="D61" s="83">
@@ -15467,7 +15472,7 @@
       <c r="T61" s="137"/>
       <c r="U61" s="115"/>
       <c r="V61" s="115" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="W61" s="115"/>
       <c r="X61" s="115"/>
@@ -15480,7 +15485,7 @@
     <row r="62" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A62" s="192"/>
       <c r="B62" s="160" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="C62" s="161"/>
       <c r="D62" s="83">
@@ -15510,7 +15515,7 @@
       <c r="T62" s="137"/>
       <c r="U62" s="115"/>
       <c r="V62" s="115" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="W62" s="115"/>
       <c r="X62" s="115"/>
@@ -15522,10 +15527,10 @@
     </row>
     <row r="63" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A63" s="190" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="B63" s="160" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="C63" s="161"/>
       <c r="D63" s="83">
@@ -15555,7 +15560,7 @@
       <c r="T63" s="137"/>
       <c r="U63" s="115"/>
       <c r="V63" s="115" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="W63" s="115"/>
       <c r="X63" s="115"/>
@@ -15568,7 +15573,7 @@
     <row r="64" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A64" s="192"/>
       <c r="B64" s="160" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="C64" s="161"/>
       <c r="D64" s="83">
@@ -15598,7 +15603,7 @@
       <c r="T64" s="137"/>
       <c r="U64" s="115"/>
       <c r="V64" s="115" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="W64" s="115"/>
       <c r="X64" s="115"/>
@@ -15610,10 +15615,10 @@
     </row>
     <row r="65" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A65" s="190" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="B65" s="160" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="C65" s="161"/>
       <c r="D65" s="83">
@@ -15643,7 +15648,7 @@
       <c r="T65" s="137"/>
       <c r="U65" s="115"/>
       <c r="V65" s="115" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="W65" s="115"/>
       <c r="X65" s="115"/>
@@ -15656,7 +15661,7 @@
     <row r="66" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A66" s="192"/>
       <c r="B66" s="160" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="C66" s="161"/>
       <c r="D66" s="83">
@@ -15686,7 +15691,7 @@
       <c r="T66" s="137"/>
       <c r="U66" s="115"/>
       <c r="V66" s="115" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="W66" s="115"/>
       <c r="X66" s="115"/>
@@ -15698,10 +15703,10 @@
     </row>
     <row r="67" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A67" s="190" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="B67" s="160" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C67" s="161"/>
       <c r="D67" s="83">
@@ -15731,7 +15736,7 @@
       <c r="T67" s="137"/>
       <c r="U67" s="115"/>
       <c r="V67" s="115" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="W67" s="115"/>
       <c r="X67" s="115"/>
@@ -15744,7 +15749,7 @@
     <row r="68" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A68" s="191"/>
       <c r="B68" s="160" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="C68" s="161"/>
       <c r="D68" s="83">
@@ -15774,7 +15779,7 @@
       <c r="T68" s="137"/>
       <c r="U68" s="115"/>
       <c r="V68" s="115" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="W68" s="115"/>
       <c r="X68" s="115"/>
@@ -15787,7 +15792,7 @@
     <row r="69" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A69" s="192"/>
       <c r="B69" s="160" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="C69" s="161"/>
       <c r="D69" s="83">
@@ -15817,7 +15822,7 @@
       <c r="T69" s="137"/>
       <c r="U69" s="115"/>
       <c r="V69" s="115" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
       <c r="W69" s="115"/>
       <c r="X69" s="115"/>
@@ -15829,10 +15834,10 @@
     </row>
     <row r="70" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="190" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="B70" s="168" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="C70" s="161"/>
       <c r="D70" s="165">
@@ -15860,7 +15865,7 @@
       <c r="T70" s="137"/>
       <c r="U70" s="115"/>
       <c r="V70" s="83" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="W70" s="115"/>
       <c r="X70" s="115"/>
@@ -15873,7 +15878,7 @@
     <row r="71" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="192"/>
       <c r="B71" s="160" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C71" s="161"/>
       <c r="D71" s="83">
@@ -15903,7 +15908,7 @@
       <c r="T71" s="137"/>
       <c r="U71" s="115"/>
       <c r="V71" s="115" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="W71" s="115"/>
       <c r="X71" s="115"/>
@@ -15915,10 +15920,10 @@
     </row>
     <row r="72" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A72" s="190" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="B72" s="160" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="C72" s="161"/>
       <c r="D72" s="83">
@@ -15948,7 +15953,7 @@
       <c r="T72" s="137"/>
       <c r="U72" s="115"/>
       <c r="V72" s="115" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="W72" s="115"/>
       <c r="X72" s="115"/>
@@ -15961,7 +15966,7 @@
     <row r="73" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A73" s="192"/>
       <c r="B73" s="160" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="C73" s="161"/>
       <c r="D73" s="83">
@@ -15991,7 +15996,7 @@
       <c r="T73" s="137"/>
       <c r="U73" s="115"/>
       <c r="V73" s="115" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="W73" s="115"/>
       <c r="X73" s="115"/>
@@ -16003,10 +16008,10 @@
     </row>
     <row r="74" spans="1:29" s="170" customFormat="1" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A74" s="190" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="B74" s="171" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="C74" s="169"/>
       <c r="D74" s="165">
@@ -16034,10 +16039,10 @@
       <c r="T74" s="167"/>
       <c r="U74" s="166"/>
       <c r="V74" s="166" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="W74" s="115" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="X74" s="166"/>
       <c r="Y74" s="166"/>
@@ -16049,7 +16054,7 @@
     <row r="75" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A75" s="191"/>
       <c r="B75" s="168" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
       <c r="C75" s="161"/>
       <c r="D75" s="165">
@@ -16077,7 +16082,7 @@
       <c r="T75" s="137"/>
       <c r="U75" s="115"/>
       <c r="V75" s="115" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="W75" s="115"/>
       <c r="X75" s="115"/>
@@ -16090,7 +16095,7 @@
     <row r="76" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A76" s="192"/>
       <c r="B76" s="168" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="C76" s="161"/>
       <c r="D76" s="165">
@@ -16120,7 +16125,7 @@
       <c r="T76" s="137"/>
       <c r="U76" s="115"/>
       <c r="V76" s="166" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="W76" s="115"/>
       <c r="X76" s="115"/>
@@ -16132,10 +16137,10 @@
     </row>
     <row r="77" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A77" s="190" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="B77" s="160" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="C77" s="161"/>
       <c r="D77" s="83">
@@ -16165,7 +16170,7 @@
       <c r="T77" s="137"/>
       <c r="U77" s="115"/>
       <c r="V77" s="115" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
       <c r="W77" s="115"/>
       <c r="X77" s="115"/>
@@ -16178,7 +16183,7 @@
     <row r="78" spans="1:29" s="170" customFormat="1" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A78" s="191"/>
       <c r="B78" s="168" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="C78" s="169"/>
       <c r="D78" s="165">
@@ -16208,7 +16213,7 @@
       <c r="T78" s="167"/>
       <c r="U78" s="166"/>
       <c r="V78" s="166" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="W78" s="166"/>
       <c r="X78" s="166"/>
@@ -16221,7 +16226,7 @@
     <row r="79" spans="1:29" s="170" customFormat="1" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A79" s="192"/>
       <c r="B79" s="168" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="C79" s="169"/>
       <c r="D79" s="83">
@@ -16249,7 +16254,7 @@
       <c r="T79" s="137"/>
       <c r="U79" s="115"/>
       <c r="V79" s="83" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="W79" s="115"/>
       <c r="X79" s="115"/>
@@ -16261,13 +16266,13 @@
     </row>
     <row r="80" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A80" s="160" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="B80" s="160" t="s">
+        <v>1704</v>
+      </c>
+      <c r="C80" s="160" t="s">
         <v>1705</v>
-      </c>
-      <c r="C80" s="160" t="s">
-        <v>1706</v>
       </c>
       <c r="D80" s="83">
         <v>5301</v>
@@ -16294,31 +16299,31 @@
       <c r="T80" s="137"/>
       <c r="U80" s="115"/>
       <c r="V80" s="115" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="W80" s="115"/>
       <c r="X80" s="115"/>
       <c r="Y80" s="115"/>
       <c r="Z80" s="115" t="s">
-        <v>1739</v>
+        <v>1738</v>
       </c>
       <c r="AA80" s="115" t="s">
-        <v>1739</v>
+        <v>1738</v>
       </c>
       <c r="AB80" s="115" t="s">
-        <v>1739</v>
+        <v>1738</v>
       </c>
       <c r="AC80" s="142"/>
     </row>
     <row r="81" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A81" s="160" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="B81" s="160" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="C81" s="160" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="D81" s="83">
         <v>5302</v>
@@ -16345,31 +16350,31 @@
       <c r="T81" s="137"/>
       <c r="U81" s="115"/>
       <c r="V81" s="115" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="W81" s="115"/>
       <c r="X81" s="115"/>
       <c r="Y81" s="115"/>
       <c r="Z81" s="115" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="AA81" s="115" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="AB81" s="115" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="AC81" s="142"/>
     </row>
     <row r="82" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A82" s="160" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="B82" s="160" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="C82" s="160" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="D82" s="83">
         <v>5303</v>
@@ -16394,31 +16399,31 @@
       <c r="T82" s="137"/>
       <c r="U82" s="115"/>
       <c r="V82" s="115" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="W82" s="115"/>
       <c r="X82" s="115"/>
       <c r="Y82" s="115"/>
       <c r="Z82" s="115" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA82" s="115" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB82" s="115" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
       <c r="AC82" s="142"/>
     </row>
     <row r="83" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A83" s="160" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B83" s="160" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="C83" s="160" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="D83" s="83">
         <v>5304</v>
@@ -16445,19 +16450,19 @@
       <c r="T83" s="137"/>
       <c r="U83" s="115"/>
       <c r="V83" s="115" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
       <c r="W83" s="115"/>
       <c r="X83" s="115"/>
       <c r="Y83" s="115"/>
       <c r="Z83" s="115" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="AA83" s="115" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="AB83" s="115" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="AC83" s="142"/>
     </row>
@@ -16625,7 +16630,7 @@
     </row>
     <row r="89" spans="1:29" s="172" customFormat="1" ht="14.25" x14ac:dyDescent="0.15">
       <c r="B89" s="118" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="C89" s="118"/>
       <c r="D89" s="118">
@@ -16646,7 +16651,7 @@
       <c r="T89" s="175"/>
       <c r="U89" s="174"/>
       <c r="V89" s="115" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="W89" s="174"/>
       <c r="X89" s="174"/>
@@ -16689,7 +16694,7 @@
     </row>
     <row r="91" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="B91" s="122" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="C91" s="122"/>
       <c r="D91" s="83">
@@ -16709,7 +16714,7 @@
       <c r="T91" s="109"/>
       <c r="U91" s="109"/>
       <c r="V91" s="115" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="W91" s="115"/>
       <c r="X91" s="140"/>
@@ -16722,7 +16727,7 @@
     <row r="92" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A92" s="172"/>
       <c r="B92" s="118" t="s">
-        <v>1889</v>
+        <v>1887</v>
       </c>
       <c r="C92" s="122"/>
       <c r="D92" s="83">
@@ -16742,7 +16747,7 @@
       <c r="T92" s="137"/>
       <c r="U92" s="109"/>
       <c r="V92" s="115" t="s">
-        <v>1891</v>
+        <v>1889</v>
       </c>
       <c r="W92" s="109"/>
       <c r="X92" s="109"/>
@@ -16761,7 +16766,7 @@
     <row r="93" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A93" s="172"/>
       <c r="B93" s="118" t="s">
-        <v>1890</v>
+        <v>1888</v>
       </c>
       <c r="C93" s="122"/>
       <c r="D93" s="83">
@@ -16781,7 +16786,7 @@
       <c r="T93" s="137"/>
       <c r="U93" s="109"/>
       <c r="V93" s="115" t="s">
-        <v>1892</v>
+        <v>1890</v>
       </c>
       <c r="W93" s="109"/>
       <c r="X93" s="109"/>
@@ -17274,7 +17279,7 @@
       <c r="T108" s="137"/>
       <c r="U108" s="115"/>
       <c r="V108" s="115" t="s">
-        <v>1842</v>
+        <v>1840</v>
       </c>
       <c r="W108" s="115"/>
       <c r="X108" s="115"/>
@@ -17331,7 +17336,7 @@
       </c>
       <c r="Y109" s="115"/>
       <c r="Z109" s="115" t="s">
-        <v>1946</v>
+        <v>1944</v>
       </c>
       <c r="AA109" s="115" t="s">
         <v>247</v>
@@ -17378,7 +17383,7 @@
       <c r="T110" s="137"/>
       <c r="U110" s="115"/>
       <c r="V110" s="115" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="W110" s="115"/>
       <c r="X110" s="115"/>
@@ -17589,7 +17594,7 @@
       <c r="T115" s="137"/>
       <c r="U115" s="115"/>
       <c r="V115" s="115" t="s">
-        <v>1952</v>
+        <v>1950</v>
       </c>
       <c r="W115" s="115"/>
       <c r="X115" s="115"/>
@@ -17608,7 +17613,7 @@
     <row r="116" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A116" s="1"/>
       <c r="B116" s="116" t="s">
-        <v>1951</v>
+        <v>1949</v>
       </c>
       <c r="C116" s="117"/>
       <c r="D116" s="83">
@@ -17636,7 +17641,7 @@
       <c r="T116" s="137"/>
       <c r="U116" s="115"/>
       <c r="V116" s="115" t="s">
-        <v>1953</v>
+        <v>1951</v>
       </c>
       <c r="W116" s="115"/>
       <c r="X116" s="115"/>
@@ -17916,7 +17921,7 @@
       <c r="X122" s="115"/>
       <c r="Y122" s="115"/>
       <c r="Z122" s="83" t="s">
-        <v>1843</v>
+        <v>1841</v>
       </c>
       <c r="AA122" s="83" t="s">
         <v>274</v>
@@ -18507,13 +18512,13 @@
       </c>
       <c r="Y135" s="115"/>
       <c r="Z135" s="115" t="s">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="AA135" s="115" t="s">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="AB135" s="115" t="s">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="AC135" s="142"/>
     </row>
@@ -19544,7 +19549,7 @@
       <c r="T159" s="137"/>
       <c r="U159" s="115"/>
       <c r="V159" s="115" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="W159" s="115"/>
       <c r="X159" s="115"/>
@@ -19559,7 +19564,7 @@
         <v>358</v>
       </c>
       <c r="B160" s="139" t="s">
-        <v>1942</v>
+        <v>1940</v>
       </c>
       <c r="C160" s="117"/>
       <c r="D160" s="83">
@@ -19589,7 +19594,7 @@
       <c r="T160" s="137"/>
       <c r="U160" s="115"/>
       <c r="V160" s="115" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="W160" s="115"/>
       <c r="X160" s="115"/>
@@ -19625,7 +19630,7 @@
       <c r="O161" s="115"/>
       <c r="P161" s="115"/>
       <c r="Q161" s="115" t="s">
-        <v>1853</v>
+        <v>1851</v>
       </c>
       <c r="R161" s="115"/>
       <c r="S161" s="137"/>
@@ -19993,7 +19998,7 @@
       <c r="T169" s="137"/>
       <c r="U169" s="115"/>
       <c r="V169" s="115" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="W169" s="115"/>
       <c r="X169" s="115"/>
@@ -20963,10 +20968,10 @@
     </row>
     <row r="192" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A192" s="1" t="s">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="B192" s="116" t="s">
-        <v>1826</v>
+        <v>1824</v>
       </c>
       <c r="C192" s="117"/>
       <c r="D192" s="83">
@@ -20996,7 +21001,7 @@
       <c r="V192" s="115"/>
       <c r="W192" s="115"/>
       <c r="X192" s="115" t="s">
-        <v>1827</v>
+        <v>1825</v>
       </c>
       <c r="Y192" s="115"/>
       <c r="Z192" s="115"/>
@@ -21006,10 +21011,10 @@
     </row>
     <row r="193" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A193" s="1" t="s">
-        <v>1828</v>
+        <v>1826</v>
       </c>
       <c r="B193" s="116" t="s">
-        <v>1829</v>
+        <v>1827</v>
       </c>
       <c r="C193" s="117"/>
       <c r="D193" s="83">
@@ -21038,7 +21043,7 @@
         <v>434</v>
       </c>
       <c r="W193" s="115" t="s">
-        <v>1830</v>
+        <v>1828</v>
       </c>
       <c r="X193" s="115"/>
       <c r="Y193" s="115"/>
@@ -21123,7 +21128,7 @@
       <c r="V195" s="115"/>
       <c r="W195" s="115"/>
       <c r="X195" s="115" t="s">
-        <v>1950</v>
+        <v>1948</v>
       </c>
       <c r="Y195" s="115"/>
       <c r="Z195" s="115"/>
@@ -21183,7 +21188,7 @@
         <v>440</v>
       </c>
       <c r="B197" s="116" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="C197" s="117"/>
       <c r="D197" s="83">
@@ -21213,7 +21218,7 @@
       <c r="T197" s="137"/>
       <c r="U197" s="115"/>
       <c r="V197" s="115" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="W197" s="115"/>
       <c r="X197" s="115"/>
@@ -22263,7 +22268,7 @@
       <c r="T221" s="137"/>
       <c r="U221" s="115"/>
       <c r="V221" s="115" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="W221" s="115"/>
       <c r="X221" s="115"/>
@@ -22318,7 +22323,7 @@
       <c r="T222" s="137"/>
       <c r="U222" s="115"/>
       <c r="V222" s="115" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="W222" s="115"/>
       <c r="X222" s="115"/>
@@ -22373,7 +22378,7 @@
       <c r="T223" s="137"/>
       <c r="U223" s="115"/>
       <c r="V223" s="115" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="W223" s="115"/>
       <c r="X223" s="115"/>
@@ -22853,13 +22858,13 @@
       <c r="X233" s="115"/>
       <c r="Y233" s="115"/>
       <c r="Z233" s="115" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="AA233" s="115" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="AB233" s="115" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="AC233" s="142"/>
     </row>
@@ -22902,13 +22907,13 @@
       <c r="T234" s="137"/>
       <c r="U234" s="115"/>
       <c r="V234" s="115" t="s">
-        <v>1846</v>
+        <v>1844</v>
       </c>
       <c r="W234" s="115"/>
       <c r="X234" s="115"/>
       <c r="Y234" s="115"/>
       <c r="Z234" s="83" t="s">
-        <v>1885</v>
+        <v>1883</v>
       </c>
       <c r="AA234" s="83" t="s">
         <v>277</v>
@@ -22957,19 +22962,19 @@
       <c r="T235" s="137"/>
       <c r="U235" s="115"/>
       <c r="V235" s="115" t="s">
-        <v>1845</v>
+        <v>1843</v>
       </c>
       <c r="W235" s="115"/>
       <c r="X235" s="115"/>
       <c r="Y235" s="115"/>
       <c r="Z235" s="115" t="s">
-        <v>1886</v>
+        <v>1884</v>
       </c>
       <c r="AA235" s="115" t="s">
-        <v>1886</v>
+        <v>1884</v>
       </c>
       <c r="AB235" s="115" t="s">
-        <v>1886</v>
+        <v>1884</v>
       </c>
       <c r="AC235" s="142"/>
     </row>
@@ -22978,7 +22983,7 @@
         <v>527</v>
       </c>
       <c r="B236" s="139" t="s">
-        <v>1881</v>
+        <v>1879</v>
       </c>
       <c r="C236" s="117"/>
       <c r="D236" s="83">
@@ -23012,17 +23017,17 @@
       <c r="V236" s="115"/>
       <c r="W236" s="115"/>
       <c r="X236" s="115" t="s">
-        <v>1880</v>
+        <v>1878</v>
       </c>
       <c r="Y236" s="115"/>
       <c r="Z236" s="115" t="s">
-        <v>1887</v>
+        <v>1885</v>
       </c>
       <c r="AA236" s="115" t="s">
-        <v>1887</v>
+        <v>1885</v>
       </c>
       <c r="AB236" s="115" t="s">
-        <v>1887</v>
+        <v>1885</v>
       </c>
       <c r="AC236" s="142"/>
     </row>
@@ -23108,19 +23113,19 @@
       <c r="T238" s="137"/>
       <c r="U238" s="115"/>
       <c r="V238" s="115" t="s">
-        <v>1879</v>
+        <v>1877</v>
       </c>
       <c r="W238" s="115"/>
       <c r="X238" s="115"/>
       <c r="Y238" s="115"/>
       <c r="Z238" s="115" t="s">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="AA238" s="115" t="s">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="AB238" s="115" t="s">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="AC238" s="142"/>
     </row>
@@ -23240,7 +23245,7 @@
       <c r="T241" s="137"/>
       <c r="U241" s="115"/>
       <c r="V241" s="115" t="s">
-        <v>1873</v>
+        <v>1871</v>
       </c>
       <c r="W241" s="115"/>
       <c r="X241" s="115"/>
@@ -23306,7 +23311,7 @@
         <v>537</v>
       </c>
       <c r="B243" s="146" t="s">
-        <v>1876</v>
+        <v>1874</v>
       </c>
       <c r="C243" s="117"/>
       <c r="D243" s="83">
@@ -23334,7 +23339,7 @@
       <c r="T243" s="137"/>
       <c r="U243" s="115"/>
       <c r="V243" s="115" t="s">
-        <v>1878</v>
+        <v>1876</v>
       </c>
       <c r="W243" s="115"/>
       <c r="X243" s="115"/>
@@ -23619,7 +23624,7 @@
         <v>556</v>
       </c>
       <c r="B250" s="146" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="C250" s="117"/>
       <c r="D250" s="83">
@@ -23655,7 +23660,7 @@
       <c r="T250" s="137"/>
       <c r="U250" s="115"/>
       <c r="V250" s="115" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="W250" s="115"/>
       <c r="X250" s="115"/>
@@ -23676,7 +23681,7 @@
         <v>556</v>
       </c>
       <c r="B251" s="146" t="s">
-        <v>1882</v>
+        <v>1880</v>
       </c>
       <c r="C251" s="117"/>
       <c r="D251" s="83">
@@ -23716,10 +23721,10 @@
     </row>
     <row r="252" spans="1:29" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A252" s="1" t="s">
-        <v>1943</v>
+        <v>1941</v>
       </c>
       <c r="B252" s="179" t="s">
-        <v>1944</v>
+        <v>1942</v>
       </c>
       <c r="C252" s="180"/>
       <c r="D252" s="181">
@@ -23749,7 +23754,7 @@
       <c r="T252" s="137"/>
       <c r="U252" s="115"/>
       <c r="V252" s="115" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="W252" s="115"/>
       <c r="X252" s="115"/>
@@ -24095,7 +24100,7 @@
       <c r="T260" s="137"/>
       <c r="U260" s="115"/>
       <c r="V260" s="115" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="W260" s="115"/>
       <c r="X260" s="115"/>
@@ -25310,7 +25315,7 @@
       <c r="T289" s="137"/>
       <c r="U289" s="115"/>
       <c r="V289" s="115" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="W289" s="115"/>
       <c r="X289" s="115"/>
@@ -26181,7 +26186,7 @@
         <v>674</v>
       </c>
       <c r="B310" s="116" t="s">
-        <v>2048</v>
+        <v>2046</v>
       </c>
       <c r="C310" s="117"/>
       <c r="D310" s="83">
@@ -26451,7 +26456,7 @@
         <v>692</v>
       </c>
       <c r="B316" s="116" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="C316" s="117"/>
       <c r="D316" s="83">
@@ -26477,7 +26482,7 @@
       <c r="T316" s="137"/>
       <c r="U316" s="115"/>
       <c r="V316" s="115" t="s">
-        <v>1815</v>
+        <v>1814</v>
       </c>
       <c r="W316" s="115"/>
       <c r="X316" s="115"/>
@@ -26563,7 +26568,7 @@
       <c r="T318" s="137"/>
       <c r="U318" s="115"/>
       <c r="V318" s="115" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="W318" s="115"/>
       <c r="X318" s="115"/>
@@ -26934,10 +26939,10 @@
     </row>
     <row r="327" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A327" s="1" t="s">
+        <v>1802</v>
+      </c>
+      <c r="B327" s="116" t="s">
         <v>1803</v>
-      </c>
-      <c r="B327" s="116" t="s">
-        <v>1804</v>
       </c>
       <c r="C327" s="117"/>
       <c r="D327" s="83">
@@ -26963,7 +26968,7 @@
       <c r="T327" s="137"/>
       <c r="U327" s="115"/>
       <c r="V327" s="115" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="W327" s="83"/>
       <c r="X327" s="115"/>
@@ -26975,10 +26980,10 @@
     </row>
     <row r="328" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A328" s="1" t="s">
-        <v>1855</v>
+        <v>1853</v>
       </c>
       <c r="B328" s="116" t="s">
-        <v>1856</v>
+        <v>1854</v>
       </c>
       <c r="C328" s="117"/>
       <c r="D328" s="83">
@@ -27004,7 +27009,7 @@
       <c r="T328" s="137"/>
       <c r="U328" s="115"/>
       <c r="V328" s="115" t="s">
-        <v>1857</v>
+        <v>1855</v>
       </c>
       <c r="W328" s="83"/>
       <c r="X328" s="115"/>
@@ -27023,7 +27028,7 @@
     <row r="329" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A329" s="1"/>
       <c r="B329" s="116" t="s">
-        <v>1858</v>
+        <v>1856</v>
       </c>
       <c r="C329" s="117"/>
       <c r="D329" s="83">
@@ -27057,28 +27062,28 @@
       <c r="T329" s="137"/>
       <c r="U329" s="115"/>
       <c r="V329" s="115" t="s">
-        <v>1864</v>
+        <v>1862</v>
       </c>
       <c r="W329" s="83"/>
       <c r="X329" s="115"/>
       <c r="Y329" s="115"/>
       <c r="Z329" s="115" t="s">
-        <v>1888</v>
+        <v>1886</v>
       </c>
       <c r="AA329" s="115" t="s">
-        <v>1888</v>
+        <v>1886</v>
       </c>
       <c r="AB329" s="115" t="s">
-        <v>1888</v>
+        <v>1886</v>
       </c>
       <c r="AC329" s="142"/>
     </row>
     <row r="330" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A330" s="1" t="s">
+        <v>1857</v>
+      </c>
+      <c r="B330" s="116" t="s">
         <v>1859</v>
-      </c>
-      <c r="B330" s="116" t="s">
-        <v>1861</v>
       </c>
       <c r="C330" s="117"/>
       <c r="D330" s="83">
@@ -27106,7 +27111,7 @@
       <c r="T330" s="137"/>
       <c r="U330" s="115"/>
       <c r="V330" s="115" t="s">
-        <v>1865</v>
+        <v>1863</v>
       </c>
       <c r="W330" s="115"/>
       <c r="X330" s="115"/>
@@ -27118,10 +27123,10 @@
     </row>
     <row r="331" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A331" s="1" t="s">
-        <v>1859</v>
+        <v>1857</v>
       </c>
       <c r="B331" s="116" t="s">
-        <v>1860</v>
+        <v>1858</v>
       </c>
       <c r="C331" s="117"/>
       <c r="D331" s="83">
@@ -27150,7 +27155,7 @@
       <c r="U331" s="115"/>
       <c r="V331" s="115"/>
       <c r="W331" s="115" t="s">
-        <v>1870</v>
+        <v>1868</v>
       </c>
       <c r="X331" s="115"/>
       <c r="Y331" s="115"/>
@@ -27161,10 +27166,10 @@
     </row>
     <row r="332" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A332" s="1" t="s">
-        <v>1859</v>
+        <v>1857</v>
       </c>
       <c r="B332" s="116" t="s">
-        <v>1862</v>
+        <v>1860</v>
       </c>
       <c r="C332" s="117"/>
       <c r="D332" s="83">
@@ -27192,7 +27197,7 @@
       <c r="T332" s="137"/>
       <c r="U332" s="115"/>
       <c r="V332" s="115" t="s">
-        <v>1866</v>
+        <v>1864</v>
       </c>
       <c r="W332" s="83"/>
       <c r="X332" s="115"/>
@@ -27204,10 +27209,10 @@
     </row>
     <row r="333" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A333" s="1" t="s">
-        <v>1859</v>
+        <v>1857</v>
       </c>
       <c r="B333" s="116" t="s">
-        <v>1863</v>
+        <v>1861</v>
       </c>
       <c r="C333" s="117"/>
       <c r="D333" s="83">
@@ -27235,7 +27240,7 @@
       <c r="T333" s="137"/>
       <c r="U333" s="115"/>
       <c r="V333" s="115" t="s">
-        <v>1868</v>
+        <v>1866</v>
       </c>
       <c r="W333" s="83"/>
       <c r="X333" s="115"/>
@@ -27247,10 +27252,10 @@
     </row>
     <row r="334" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A334" s="1" t="s">
-        <v>1859</v>
+        <v>1857</v>
       </c>
       <c r="B334" s="116" t="s">
-        <v>1867</v>
+        <v>1865</v>
       </c>
       <c r="C334" s="117"/>
       <c r="D334" s="83">
@@ -27278,7 +27283,7 @@
       <c r="T334" s="137"/>
       <c r="U334" s="115"/>
       <c r="V334" s="115" t="s">
-        <v>1869</v>
+        <v>1867</v>
       </c>
       <c r="W334" s="83"/>
       <c r="X334" s="115"/>
@@ -27290,10 +27295,10 @@
     </row>
     <row r="335" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A335" s="1" t="s">
-        <v>1954</v>
+        <v>1952</v>
       </c>
       <c r="B335" s="116" t="s">
-        <v>1955</v>
+        <v>1953</v>
       </c>
       <c r="C335" s="117"/>
       <c r="D335" s="83">
@@ -27321,7 +27326,7 @@
       <c r="T335" s="137"/>
       <c r="U335" s="115"/>
       <c r="V335" s="115" t="s">
-        <v>1815</v>
+        <v>1814</v>
       </c>
       <c r="W335" s="115"/>
       <c r="X335" s="115"/>
@@ -27334,7 +27339,7 @@
     <row r="336" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A336" s="1"/>
       <c r="B336" s="116" t="s">
-        <v>1905</v>
+        <v>1903</v>
       </c>
       <c r="C336" s="117"/>
       <c r="D336" s="83">
@@ -27372,24 +27377,24 @@
       <c r="V336" s="115"/>
       <c r="W336" s="115"/>
       <c r="X336" s="115" t="s">
-        <v>1894</v>
+        <v>1892</v>
       </c>
       <c r="Y336" s="115"/>
       <c r="Z336" s="115" t="s">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="AA336" s="115" t="s">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="AB336" s="115" t="s">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="AC336" s="142"/>
     </row>
     <row r="337" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A337" s="1"/>
       <c r="B337" s="116" t="s">
-        <v>1906</v>
+        <v>1904</v>
       </c>
       <c r="C337" s="117"/>
       <c r="D337" s="83">
@@ -27423,26 +27428,26 @@
       <c r="T337" s="177"/>
       <c r="U337" s="115"/>
       <c r="V337" s="115" t="s">
-        <v>1972</v>
+        <v>1970</v>
       </c>
       <c r="W337" s="115"/>
       <c r="X337" s="115"/>
       <c r="Y337" s="115"/>
       <c r="Z337" s="115" t="s">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="AA337" s="115" t="s">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="AB337" s="115" t="s">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="AC337" s="142"/>
     </row>
     <row r="338" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A338" s="1"/>
       <c r="B338" s="116" t="s">
-        <v>1907</v>
+        <v>1905</v>
       </c>
       <c r="C338" s="117"/>
       <c r="D338" s="83">
@@ -27476,26 +27481,26 @@
       <c r="T338" s="177"/>
       <c r="U338" s="115"/>
       <c r="V338" s="115" t="s">
-        <v>1979</v>
+        <v>1977</v>
       </c>
       <c r="W338" s="115"/>
       <c r="X338" s="115"/>
       <c r="Y338" s="115"/>
       <c r="Z338" s="115" t="s">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="AA338" s="115" t="s">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="AB338" s="115" t="s">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="AC338" s="142"/>
     </row>
     <row r="339" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A339" s="1"/>
       <c r="B339" s="116" t="s">
-        <v>1908</v>
+        <v>1906</v>
       </c>
       <c r="C339" s="117"/>
       <c r="D339" s="83">
@@ -27529,28 +27534,28 @@
       <c r="T339" s="177"/>
       <c r="U339" s="115"/>
       <c r="V339" s="115" t="s">
-        <v>1980</v>
+        <v>1978</v>
       </c>
       <c r="W339" s="115"/>
       <c r="X339" s="115"/>
       <c r="Y339" s="115"/>
       <c r="Z339" s="115" t="s">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="AA339" s="115" t="s">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="AB339" s="115" t="s">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="AC339" s="142"/>
     </row>
     <row r="340" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A340" s="1" t="s">
+        <v>1930</v>
+      </c>
+      <c r="B340" s="116" t="s">
         <v>1932</v>
-      </c>
-      <c r="B340" s="116" t="s">
-        <v>1934</v>
       </c>
       <c r="C340" s="117"/>
       <c r="D340" s="83">
@@ -27579,7 +27584,7 @@
       <c r="U340" s="115"/>
       <c r="V340" s="83"/>
       <c r="W340" s="115" t="s">
-        <v>1939</v>
+        <v>1937</v>
       </c>
       <c r="X340" s="115"/>
       <c r="Y340" s="115"/>
@@ -27590,10 +27595,10 @@
     </row>
     <row r="341" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A341" s="1" t="s">
+        <v>1931</v>
+      </c>
+      <c r="B341" s="116" t="s">
         <v>1933</v>
-      </c>
-      <c r="B341" s="116" t="s">
-        <v>1935</v>
       </c>
       <c r="C341" s="117"/>
       <c r="D341" s="83">
@@ -27621,7 +27626,7 @@
       <c r="T341" s="177"/>
       <c r="U341" s="115"/>
       <c r="V341" s="115" t="s">
-        <v>1940</v>
+        <v>1938</v>
       </c>
       <c r="W341" s="115"/>
       <c r="X341" s="115"/>
@@ -27633,10 +27638,10 @@
     </row>
     <row r="342" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A342" s="1" t="s">
-        <v>1933</v>
+        <v>1931</v>
       </c>
       <c r="B342" s="116" t="s">
-        <v>1936</v>
+        <v>1934</v>
       </c>
       <c r="C342" s="117"/>
       <c r="D342" s="83">
@@ -27664,7 +27669,7 @@
       <c r="T342" s="177"/>
       <c r="U342" s="115"/>
       <c r="V342" s="115" t="s">
-        <v>1938</v>
+        <v>1936</v>
       </c>
       <c r="W342" s="115"/>
       <c r="X342" s="115"/>
@@ -27676,10 +27681,10 @@
     </row>
     <row r="343" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A343" s="1" t="s">
-        <v>1933</v>
+        <v>1931</v>
       </c>
       <c r="B343" s="116" t="s">
-        <v>1937</v>
+        <v>1935</v>
       </c>
       <c r="C343" s="117"/>
       <c r="D343" s="83">
@@ -27709,7 +27714,7 @@
       <c r="T343" s="177"/>
       <c r="U343" s="115"/>
       <c r="V343" s="115" t="s">
-        <v>1981</v>
+        <v>1979</v>
       </c>
       <c r="W343" s="115"/>
       <c r="X343" s="115"/>
@@ -27721,10 +27726,10 @@
     </row>
     <row r="344" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A344" s="1" t="s">
-        <v>1947</v>
+        <v>1945</v>
       </c>
       <c r="B344" s="116" t="s">
-        <v>1948</v>
+        <v>1946</v>
       </c>
       <c r="C344" s="117"/>
       <c r="D344" s="83">
@@ -27752,7 +27757,7 @@
       <c r="T344" s="177"/>
       <c r="U344" s="115"/>
       <c r="V344" s="115" t="s">
-        <v>1949</v>
+        <v>1947</v>
       </c>
       <c r="W344" s="115"/>
       <c r="X344" s="115"/>
@@ -27764,10 +27769,10 @@
     </row>
     <row r="345" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A345" s="1" t="s">
-        <v>1956</v>
+        <v>1954</v>
       </c>
       <c r="B345" s="116" t="s">
-        <v>1957</v>
+        <v>1955</v>
       </c>
       <c r="C345" s="117"/>
       <c r="D345" s="83">
@@ -27795,7 +27800,7 @@
       <c r="T345" s="137"/>
       <c r="U345" s="115"/>
       <c r="V345" s="115" t="s">
-        <v>1958</v>
+        <v>1956</v>
       </c>
       <c r="W345" s="115"/>
       <c r="X345" s="115"/>
@@ -27807,10 +27812,10 @@
     </row>
     <row r="346" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A346" s="1" t="s">
-        <v>1959</v>
+        <v>1957</v>
       </c>
       <c r="B346" s="116" t="s">
-        <v>1960</v>
+        <v>1958</v>
       </c>
       <c r="C346" s="117"/>
       <c r="D346" s="83">
@@ -27838,7 +27843,7 @@
       <c r="T346" s="177"/>
       <c r="U346" s="115"/>
       <c r="V346" s="115" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="W346" s="115"/>
       <c r="X346" s="115"/>
@@ -27850,10 +27855,10 @@
     </row>
     <row r="347" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A347" s="1" t="s">
+        <v>1957</v>
+      </c>
+      <c r="B347" s="116" t="s">
         <v>1959</v>
-      </c>
-      <c r="B347" s="116" t="s">
-        <v>1961</v>
       </c>
       <c r="C347" s="117"/>
       <c r="D347" s="83">
@@ -27881,7 +27886,7 @@
       <c r="T347" s="177"/>
       <c r="U347" s="115"/>
       <c r="V347" s="115" t="s">
-        <v>1963</v>
+        <v>1961</v>
       </c>
       <c r="W347" s="115"/>
       <c r="X347" s="115"/>
@@ -27893,10 +27898,10 @@
     </row>
     <row r="348" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A348" s="1" t="s">
-        <v>1959</v>
+        <v>1957</v>
       </c>
       <c r="B348" s="116" t="s">
-        <v>1962</v>
+        <v>1960</v>
       </c>
       <c r="C348" s="117"/>
       <c r="D348" s="83">
@@ -27925,7 +27930,7 @@
       <c r="U348" s="115"/>
       <c r="V348" s="115"/>
       <c r="W348" s="115" t="s">
-        <v>2001</v>
+        <v>1999</v>
       </c>
       <c r="X348" s="115"/>
       <c r="Y348" s="115"/>
@@ -27936,10 +27941,10 @@
     </row>
     <row r="349" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A349" s="1" t="s">
-        <v>1964</v>
+        <v>1962</v>
       </c>
       <c r="B349" s="116" t="s">
-        <v>1965</v>
+        <v>1963</v>
       </c>
       <c r="C349" s="117"/>
       <c r="D349" s="83">
@@ -27967,7 +27972,7 @@
       <c r="T349" s="177"/>
       <c r="U349" s="115"/>
       <c r="V349" s="115" t="s">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="W349" s="115"/>
       <c r="X349" s="83"/>
@@ -27979,10 +27984,10 @@
     </row>
     <row r="350" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A350" s="1" t="s">
+        <v>1962</v>
+      </c>
+      <c r="B350" s="116" t="s">
         <v>1964</v>
-      </c>
-      <c r="B350" s="116" t="s">
-        <v>1966</v>
       </c>
       <c r="C350" s="117"/>
       <c r="D350" s="83">
@@ -28010,7 +28015,7 @@
       <c r="T350" s="177"/>
       <c r="U350" s="115"/>
       <c r="V350" s="115" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="W350" s="115"/>
       <c r="X350" s="115"/>
@@ -28022,10 +28027,10 @@
     </row>
     <row r="351" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A351" s="1" t="s">
-        <v>1964</v>
+        <v>1962</v>
       </c>
       <c r="B351" s="116" t="s">
-        <v>1967</v>
+        <v>1965</v>
       </c>
       <c r="C351" s="117"/>
       <c r="D351" s="83">
@@ -28053,7 +28058,7 @@
       <c r="T351" s="177"/>
       <c r="U351" s="115"/>
       <c r="V351" s="115" t="s">
-        <v>1969</v>
+        <v>1967</v>
       </c>
       <c r="W351" s="115"/>
       <c r="X351" s="115"/>
@@ -28065,10 +28070,10 @@
     </row>
     <row r="352" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A352" s="1" t="s">
-        <v>1964</v>
+        <v>1962</v>
       </c>
       <c r="B352" s="116" t="s">
-        <v>1982</v>
+        <v>1980</v>
       </c>
       <c r="C352" s="117"/>
       <c r="D352" s="83">
@@ -28100,7 +28105,7 @@
       <c r="V352" s="115"/>
       <c r="W352" s="115"/>
       <c r="X352" s="115" t="s">
-        <v>1968</v>
+        <v>1966</v>
       </c>
       <c r="Y352" s="115"/>
       <c r="Z352" s="83"/>
@@ -28111,7 +28116,7 @@
     <row r="353" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A353" s="1"/>
       <c r="B353" s="143" t="s">
-        <v>1983</v>
+        <v>1981</v>
       </c>
       <c r="C353" s="143"/>
       <c r="D353" s="118">
@@ -28147,10 +28152,10 @@
     </row>
     <row r="354" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A354" s="1" t="s">
-        <v>1971</v>
+        <v>1969</v>
       </c>
       <c r="B354" s="116" t="s">
-        <v>1967</v>
+        <v>1965</v>
       </c>
       <c r="C354" s="117"/>
       <c r="D354" s="83">
@@ -28180,7 +28185,7 @@
       <c r="T354" s="177"/>
       <c r="U354" s="115"/>
       <c r="V354" s="115" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="W354" s="115"/>
       <c r="X354" s="115"/>
@@ -28193,7 +28198,7 @@
     <row r="355" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A355" s="1"/>
       <c r="B355" s="116" t="s">
-        <v>1976</v>
+        <v>1974</v>
       </c>
       <c r="C355" s="117"/>
       <c r="D355" s="83">
@@ -28227,26 +28232,26 @@
       <c r="T355" s="177"/>
       <c r="U355" s="115"/>
       <c r="V355" s="115" t="s">
-        <v>1973</v>
+        <v>1971</v>
       </c>
       <c r="W355" s="115"/>
       <c r="X355" s="115"/>
       <c r="Y355" s="115"/>
       <c r="Z355" s="115" t="s">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="AA355" s="115" t="s">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="AB355" s="115" t="s">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="AC355" s="142"/>
     </row>
     <row r="356" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A356" s="1"/>
       <c r="B356" s="116" t="s">
-        <v>1976</v>
+        <v>1974</v>
       </c>
       <c r="C356" s="117"/>
       <c r="D356" s="83">
@@ -28280,26 +28285,26 @@
       <c r="T356" s="177"/>
       <c r="U356" s="115"/>
       <c r="V356" s="115" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="W356" s="115"/>
       <c r="X356" s="115"/>
       <c r="Y356" s="115"/>
       <c r="Z356" s="115" t="s">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="AA356" s="115" t="s">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="AB356" s="115" t="s">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="AC356" s="142"/>
     </row>
     <row r="357" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A357" s="1"/>
       <c r="B357" s="116" t="s">
-        <v>1976</v>
+        <v>1974</v>
       </c>
       <c r="C357" s="117"/>
       <c r="D357" s="83">
@@ -28333,26 +28338,26 @@
       <c r="T357" s="177"/>
       <c r="U357" s="115"/>
       <c r="V357" s="115" t="s">
-        <v>1974</v>
+        <v>1972</v>
       </c>
       <c r="W357" s="115"/>
       <c r="X357" s="115"/>
       <c r="Y357" s="115"/>
       <c r="Z357" s="115" t="s">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="AA357" s="115" t="s">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="AB357" s="115" t="s">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="AC357" s="142"/>
     </row>
     <row r="358" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A358" s="1"/>
       <c r="B358" s="116" t="s">
-        <v>1977</v>
+        <v>1975</v>
       </c>
       <c r="C358" s="117"/>
       <c r="D358" s="83">
@@ -28386,26 +28391,26 @@
       <c r="T358" s="177"/>
       <c r="U358" s="115"/>
       <c r="V358" s="115" t="s">
-        <v>1978</v>
+        <v>1976</v>
       </c>
       <c r="W358" s="115"/>
       <c r="X358" s="115"/>
       <c r="Y358" s="115"/>
       <c r="Z358" s="115" t="s">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="AA358" s="115" t="s">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="AB358" s="115" t="s">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="AC358" s="142"/>
     </row>
     <row r="359" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A359" s="1"/>
       <c r="B359" s="116" t="s">
-        <v>2030</v>
+        <v>2028</v>
       </c>
       <c r="C359" s="117"/>
       <c r="D359" s="83">
@@ -28433,7 +28438,7 @@
       <c r="T359" s="177"/>
       <c r="U359" s="115"/>
       <c r="V359" s="115" t="s">
-        <v>2029</v>
+        <v>2027</v>
       </c>
       <c r="W359" s="83"/>
       <c r="X359" s="115"/>
@@ -28446,7 +28451,7 @@
     <row r="360" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A360" s="1"/>
       <c r="B360" s="116" t="s">
-        <v>1893</v>
+        <v>1891</v>
       </c>
       <c r="C360" s="117"/>
       <c r="D360" s="83">
@@ -28474,7 +28479,7 @@
       <c r="T360" s="177"/>
       <c r="U360" s="115"/>
       <c r="V360" s="115" t="s">
-        <v>1894</v>
+        <v>1892</v>
       </c>
       <c r="W360" s="83"/>
       <c r="X360" s="115"/>
@@ -28719,7 +28724,7 @@
       <c r="T368" s="139"/>
       <c r="U368" s="83"/>
       <c r="V368" s="115" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="W368" s="83"/>
       <c r="X368" s="83"/>
@@ -28813,7 +28818,7 @@
       <c r="V370" s="115"/>
       <c r="W370" s="115"/>
       <c r="X370" s="115" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
       <c r="Y370" s="115"/>
       <c r="Z370" s="83" t="s">
@@ -29369,10 +29374,10 @@
     </row>
     <row r="383" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A383" s="1" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="B383" s="116" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="C383" s="117"/>
       <c r="D383" s="83">
@@ -29398,7 +29403,7 @@
       <c r="T383" s="137"/>
       <c r="U383" s="115"/>
       <c r="V383" s="115" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="W383" s="115"/>
       <c r="X383" s="115"/>
@@ -29410,10 +29415,10 @@
     </row>
     <row r="384" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A384" s="1" t="s">
+        <v>1662</v>
+      </c>
+      <c r="B384" s="116" t="s">
         <v>1663</v>
-      </c>
-      <c r="B384" s="116" t="s">
-        <v>1664</v>
       </c>
       <c r="C384" s="117"/>
       <c r="D384" s="83">
@@ -29439,7 +29444,7 @@
       <c r="T384" s="137"/>
       <c r="U384" s="115"/>
       <c r="V384" s="115" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="W384" s="115"/>
       <c r="X384" s="115"/>
@@ -29451,10 +29456,10 @@
     </row>
     <row r="385" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A385" s="1" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
       <c r="B385" s="116" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="C385" s="117"/>
       <c r="D385" s="83">
@@ -29480,7 +29485,7 @@
       <c r="T385" s="137"/>
       <c r="U385" s="115"/>
       <c r="V385" s="115" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="W385" s="115"/>
       <c r="X385" s="115"/>
@@ -30525,7 +30530,7 @@
       <c r="X408" s="115"/>
       <c r="Y408" s="115"/>
       <c r="Z408" s="115" t="s">
-        <v>1945</v>
+        <v>1943</v>
       </c>
       <c r="AA408" s="115" t="s">
         <v>281</v>
@@ -30728,7 +30733,7 @@
         <v>808</v>
       </c>
       <c r="B413" s="116" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="C413" s="117"/>
       <c r="D413" s="83">
@@ -30754,7 +30759,7 @@
       <c r="T413" s="137"/>
       <c r="U413" s="115"/>
       <c r="V413" s="83" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="W413" s="115"/>
       <c r="X413" s="115"/>
@@ -30769,7 +30774,7 @@
         <v>808</v>
       </c>
       <c r="B414" s="116" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="C414" s="117"/>
       <c r="D414" s="83">
@@ -30795,7 +30800,7 @@
       <c r="T414" s="137"/>
       <c r="U414" s="115"/>
       <c r="V414" s="83" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="W414" s="115"/>
       <c r="X414" s="115"/>
@@ -30934,7 +30939,7 @@
       <c r="T417" s="137"/>
       <c r="U417" s="115"/>
       <c r="V417" s="115" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="W417" s="115"/>
       <c r="X417" s="115"/>
@@ -30996,7 +31001,7 @@
         <v>808</v>
       </c>
       <c r="B419" s="116" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
       <c r="C419" s="117"/>
       <c r="D419" s="83">
@@ -31022,7 +31027,7 @@
       <c r="T419" s="137"/>
       <c r="U419" s="115"/>
       <c r="V419" s="83" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="W419" s="115"/>
       <c r="X419" s="115"/>
@@ -31063,7 +31068,7 @@
       <c r="T420" s="137"/>
       <c r="U420" s="115"/>
       <c r="V420" s="83" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="W420" s="115"/>
       <c r="X420" s="115"/>
@@ -31292,7 +31297,7 @@
       <c r="T425" s="137"/>
       <c r="U425" s="115"/>
       <c r="V425" s="83" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="W425" s="115"/>
       <c r="X425" s="115"/>
@@ -31333,7 +31338,7 @@
       <c r="T426" s="137"/>
       <c r="U426" s="115"/>
       <c r="V426" s="115" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="W426" s="115"/>
       <c r="X426" s="115"/>
@@ -31354,7 +31359,7 @@
         <v>808</v>
       </c>
       <c r="B427" s="116" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="C427" s="117"/>
       <c r="D427" s="83">
@@ -31378,7 +31383,7 @@
       <c r="T427" s="137"/>
       <c r="U427" s="115"/>
       <c r="V427" s="83" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="W427" s="115"/>
       <c r="X427" s="115"/>
@@ -31393,7 +31398,7 @@
         <v>808</v>
       </c>
       <c r="B428" s="116" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
       <c r="C428" s="117"/>
       <c r="D428" s="83">
@@ -31417,7 +31422,7 @@
       <c r="T428" s="137"/>
       <c r="U428" s="115"/>
       <c r="V428" s="83" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="W428" s="115"/>
       <c r="X428" s="115"/>
@@ -31432,7 +31437,7 @@
         <v>808</v>
       </c>
       <c r="B429" s="116" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="C429" s="117"/>
       <c r="D429" s="83">
@@ -31456,7 +31461,7 @@
       <c r="T429" s="137"/>
       <c r="U429" s="115"/>
       <c r="V429" s="83" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="W429" s="115"/>
       <c r="X429" s="115"/>
@@ -31468,10 +31473,10 @@
     </row>
     <row r="430" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A430" s="139" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="B430" s="116" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="C430" s="117"/>
       <c r="D430" s="83">
@@ -31507,13 +31512,13 @@
       <c r="T430" s="137"/>
       <c r="U430" s="115"/>
       <c r="V430" s="115" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="W430" s="115"/>
       <c r="X430" s="115"/>
       <c r="Y430" s="115"/>
       <c r="Z430" s="115" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="AA430" s="115" t="s">
         <v>85</v>
@@ -31528,7 +31533,7 @@
         <v>808</v>
       </c>
       <c r="B431" s="116" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="C431" s="117"/>
       <c r="D431" s="83">
@@ -31564,7 +31569,7 @@
       <c r="T431" s="137"/>
       <c r="U431" s="115"/>
       <c r="V431" s="115" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="W431" s="115"/>
       <c r="X431" s="115"/>
@@ -31585,7 +31590,7 @@
         <v>808</v>
       </c>
       <c r="B432" s="116" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="C432" s="117"/>
       <c r="D432" s="83">
@@ -31621,7 +31626,7 @@
       <c r="T432" s="137"/>
       <c r="U432" s="115"/>
       <c r="V432" s="115" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="W432" s="115"/>
       <c r="X432" s="115"/>
@@ -31642,7 +31647,7 @@
         <v>808</v>
       </c>
       <c r="B433" s="116" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="C433" s="117"/>
       <c r="D433" s="83">
@@ -31668,7 +31673,7 @@
       <c r="T433" s="137"/>
       <c r="U433" s="115"/>
       <c r="V433" s="115" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="W433" s="83"/>
       <c r="X433" s="115"/>
@@ -31683,7 +31688,7 @@
         <v>808</v>
       </c>
       <c r="B434" s="116" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="C434" s="117"/>
       <c r="D434" s="83">
@@ -31713,7 +31718,7 @@
       <c r="T434" s="137"/>
       <c r="U434" s="115"/>
       <c r="V434" s="115" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="W434" s="83"/>
       <c r="X434" s="115"/>
@@ -31762,7 +31767,7 @@
       <c r="T435" s="137"/>
       <c r="U435" s="115"/>
       <c r="V435" s="115" t="s">
-        <v>2055</v>
+        <v>2053</v>
       </c>
       <c r="W435" s="115"/>
       <c r="X435" s="115"/>
@@ -31777,7 +31782,7 @@
         <v>835</v>
       </c>
       <c r="B436" s="116" t="s">
-        <v>2054</v>
+        <v>2052</v>
       </c>
       <c r="C436" s="117"/>
       <c r="D436" s="83">
@@ -31803,7 +31808,7 @@
       <c r="T436" s="137"/>
       <c r="U436" s="115"/>
       <c r="V436" s="83" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="W436" s="115"/>
       <c r="X436" s="115"/>
@@ -32077,7 +32082,7 @@
       <c r="T442" s="137"/>
       <c r="U442" s="115"/>
       <c r="V442" s="115" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="W442" s="115"/>
       <c r="X442" s="115"/>
@@ -32312,7 +32317,7 @@
       <c r="V447" s="83"/>
       <c r="W447" s="115"/>
       <c r="X447" s="115" t="s">
-        <v>1841</v>
+        <v>1839</v>
       </c>
       <c r="Y447" s="115"/>
       <c r="Z447" s="83"/>
@@ -32325,7 +32330,7 @@
         <v>835</v>
       </c>
       <c r="B448" s="116" t="s">
-        <v>2049</v>
+        <v>2047</v>
       </c>
       <c r="C448" s="117"/>
       <c r="D448" s="83">
@@ -32458,7 +32463,7 @@
         <v>835</v>
       </c>
       <c r="B451" s="116" t="s">
-        <v>2050</v>
+        <v>2048</v>
       </c>
       <c r="C451" s="117"/>
       <c r="D451" s="83">
@@ -32782,7 +32787,7 @@
     </row>
     <row r="458" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A458" s="139" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="B458" s="116" t="s">
         <v>641</v>
@@ -32832,10 +32837,10 @@
     </row>
     <row r="459" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A459" s="139" t="s">
+        <v>1651</v>
+      </c>
+      <c r="B459" s="116" t="s">
         <v>1652</v>
-      </c>
-      <c r="B459" s="116" t="s">
-        <v>1653</v>
       </c>
       <c r="D459" s="83">
         <v>41025</v>
@@ -32876,7 +32881,7 @@
       <c r="T459" s="137"/>
       <c r="U459" s="115"/>
       <c r="V459" s="115" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="W459" s="115"/>
       <c r="X459" s="115"/>
@@ -32894,10 +32899,10 @@
     </row>
     <row r="460" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A460" s="139" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="B460" s="116" t="s">
-        <v>1839</v>
+        <v>1837</v>
       </c>
       <c r="D460" s="83">
         <v>41026</v>
@@ -32938,7 +32943,7 @@
       <c r="T460" s="137"/>
       <c r="U460" s="115"/>
       <c r="V460" s="115" t="s">
-        <v>1831</v>
+        <v>1829</v>
       </c>
       <c r="W460" s="115"/>
       <c r="X460" s="115"/>
@@ -32956,10 +32961,10 @@
     </row>
     <row r="461" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A461" s="139" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="B461" s="116" t="s">
-        <v>1838</v>
+        <v>1836</v>
       </c>
       <c r="D461" s="83">
         <v>41027</v>
@@ -32986,7 +32991,7 @@
       <c r="V461" s="83"/>
       <c r="W461" s="115"/>
       <c r="X461" s="115" t="s">
-        <v>1837</v>
+        <v>1835</v>
       </c>
       <c r="Y461" s="115"/>
       <c r="Z461" s="83"/>
@@ -32996,10 +33001,10 @@
     </row>
     <row r="462" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A462" s="139" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="B462" s="116" t="s">
-        <v>1832</v>
+        <v>1830</v>
       </c>
       <c r="D462" s="83">
         <v>41028</v>
@@ -33024,7 +33029,7 @@
       <c r="T462" s="137"/>
       <c r="U462" s="115"/>
       <c r="V462" s="115" t="s">
-        <v>1833</v>
+        <v>1831</v>
       </c>
       <c r="W462" s="115"/>
       <c r="X462" s="115"/>
@@ -33036,10 +33041,10 @@
     </row>
     <row r="463" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A463" s="139" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="B463" s="116" t="s">
-        <v>1834</v>
+        <v>1832</v>
       </c>
       <c r="D463" s="83">
         <v>41029</v>
@@ -33068,7 +33073,7 @@
       <c r="V463" s="115"/>
       <c r="W463" s="115"/>
       <c r="X463" s="115" t="s">
-        <v>1836</v>
+        <v>1834</v>
       </c>
       <c r="Y463" s="115"/>
       <c r="Z463" s="83"/>
@@ -33078,10 +33083,10 @@
     </row>
     <row r="464" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A464" s="139" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="B464" s="116" t="s">
-        <v>1835</v>
+        <v>1833</v>
       </c>
       <c r="D464" s="83">
         <v>41030</v>
@@ -33106,7 +33111,7 @@
       <c r="T464" s="137"/>
       <c r="U464" s="115"/>
       <c r="V464" s="115" t="s">
-        <v>1840</v>
+        <v>1838</v>
       </c>
       <c r="W464" s="115"/>
       <c r="X464" s="115"/>
@@ -33124,10 +33129,10 @@
     </row>
     <row r="465" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A465" s="139" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="B465" s="116" t="s">
-        <v>1895</v>
+        <v>1893</v>
       </c>
       <c r="D465" s="83">
         <v>41031</v>
@@ -33152,7 +33157,7 @@
       <c r="T465" s="177"/>
       <c r="U465" s="115"/>
       <c r="V465" s="115" t="s">
-        <v>1896</v>
+        <v>1894</v>
       </c>
       <c r="W465" s="115"/>
       <c r="X465" s="115"/>
@@ -33164,10 +33169,10 @@
     </row>
     <row r="466" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A466" s="139" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="B466" s="116" t="s">
-        <v>1897</v>
+        <v>1895</v>
       </c>
       <c r="D466" s="83">
         <v>41032</v>
@@ -33202,7 +33207,7 @@
       <c r="T466" s="177"/>
       <c r="U466" s="115"/>
       <c r="V466" s="115" t="s">
-        <v>1899</v>
+        <v>1897</v>
       </c>
       <c r="W466" s="115"/>
       <c r="X466" s="115"/>
@@ -33214,10 +33219,10 @@
     </row>
     <row r="467" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A467" s="139" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="B467" s="116" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="D467" s="83">
         <v>41033</v>
@@ -33244,7 +33249,7 @@
       <c r="T467" s="177"/>
       <c r="U467" s="115"/>
       <c r="V467" s="115" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="W467" s="115"/>
       <c r="X467" s="115"/>
@@ -33256,10 +33261,10 @@
     </row>
     <row r="468" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A468" s="139" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="B468" s="116" t="s">
-        <v>1901</v>
+        <v>1899</v>
       </c>
       <c r="D468" s="83">
         <v>41034</v>
@@ -33284,7 +33289,7 @@
       <c r="T468" s="177"/>
       <c r="U468" s="115"/>
       <c r="V468" s="115" t="s">
-        <v>1902</v>
+        <v>1900</v>
       </c>
       <c r="W468" s="115"/>
       <c r="X468" s="115"/>
@@ -33296,10 +33301,10 @@
     </row>
     <row r="469" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A469" s="139" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="B469" s="116" t="s">
-        <v>1903</v>
+        <v>1901</v>
       </c>
       <c r="D469" s="83">
         <v>41035</v>
@@ -33324,7 +33329,7 @@
       <c r="T469" s="177"/>
       <c r="U469" s="115"/>
       <c r="V469" s="115" t="s">
-        <v>1904</v>
+        <v>1902</v>
       </c>
       <c r="W469" s="115"/>
       <c r="X469" s="115"/>
@@ -33336,10 +33341,10 @@
     </row>
     <row r="470" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A470" s="139" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="B470" s="116" t="s">
-        <v>1909</v>
+        <v>1907</v>
       </c>
       <c r="D470" s="83">
         <v>41036</v>
@@ -33364,7 +33369,7 @@
       <c r="T470" s="177"/>
       <c r="U470" s="115"/>
       <c r="V470" s="115" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="W470" s="115"/>
       <c r="X470" s="115"/>
@@ -33376,10 +33381,10 @@
     </row>
     <row r="471" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A471" s="139" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="B471" s="116" t="s">
-        <v>1910</v>
+        <v>1908</v>
       </c>
       <c r="D471" s="83">
         <v>41037</v>
@@ -33404,7 +33409,7 @@
       <c r="T471" s="177"/>
       <c r="U471" s="115"/>
       <c r="V471" s="115" t="s">
-        <v>1911</v>
+        <v>1909</v>
       </c>
       <c r="W471" s="115"/>
       <c r="X471" s="115"/>
@@ -33416,10 +33421,10 @@
     </row>
     <row r="472" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A472" s="139" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="B472" s="116" t="s">
-        <v>1913</v>
+        <v>1911</v>
       </c>
       <c r="D472" s="83">
         <v>41038</v>
@@ -33450,7 +33455,7 @@
       <c r="V472" s="115"/>
       <c r="W472" s="115"/>
       <c r="X472" s="115" t="s">
-        <v>1912</v>
+        <v>1910</v>
       </c>
       <c r="Y472" s="115"/>
       <c r="Z472" s="83"/>
@@ -33460,10 +33465,10 @@
     </row>
     <row r="473" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A473" s="139" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="B473" s="116" t="s">
-        <v>1914</v>
+        <v>1912</v>
       </c>
       <c r="D473" s="83">
         <v>41039</v>
@@ -33502,10 +33507,10 @@
     </row>
     <row r="474" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A474" s="139" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="B474" s="116" t="s">
-        <v>1915</v>
+        <v>1913</v>
       </c>
       <c r="D474" s="83">
         <v>41040</v>
@@ -33530,7 +33535,7 @@
       <c r="T474" s="177"/>
       <c r="U474" s="115"/>
       <c r="V474" s="115" t="s">
-        <v>1929</v>
+        <v>1927</v>
       </c>
       <c r="W474" s="115"/>
       <c r="X474" s="115"/>
@@ -33542,10 +33547,10 @@
     </row>
     <row r="475" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A475" s="139" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="B475" s="116" t="s">
-        <v>1917</v>
+        <v>1915</v>
       </c>
       <c r="D475" s="83">
         <v>41041</v>
@@ -33580,7 +33585,7 @@
       <c r="T475" s="177"/>
       <c r="U475" s="115"/>
       <c r="V475" s="115" t="s">
-        <v>1919</v>
+        <v>1917</v>
       </c>
       <c r="W475" s="115"/>
       <c r="X475" s="115"/>
@@ -33592,10 +33597,10 @@
     </row>
     <row r="476" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A476" s="139" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="B476" s="116" t="s">
-        <v>1918</v>
+        <v>1916</v>
       </c>
       <c r="D476" s="83">
         <v>41042</v>
@@ -33630,7 +33635,7 @@
       <c r="T476" s="177"/>
       <c r="U476" s="115"/>
       <c r="V476" s="115" t="s">
-        <v>1920</v>
+        <v>1918</v>
       </c>
       <c r="W476" s="115"/>
       <c r="X476" s="115"/>
@@ -33642,10 +33647,10 @@
     </row>
     <row r="477" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A477" s="139" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="B477" s="116" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="D477" s="83">
         <v>41043</v>
@@ -33676,7 +33681,7 @@
       <c r="T477" s="177"/>
       <c r="U477" s="115"/>
       <c r="V477" s="115" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="W477" s="115"/>
       <c r="X477" s="115"/>
@@ -33688,10 +33693,10 @@
     </row>
     <row r="478" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A478" s="139" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="B478" s="116" t="s">
-        <v>1922</v>
+        <v>1920</v>
       </c>
       <c r="D478" s="83">
         <v>41044</v>
@@ -33716,7 +33721,7 @@
       <c r="T478" s="177"/>
       <c r="U478" s="115"/>
       <c r="V478" s="115" t="s">
-        <v>1926</v>
+        <v>1924</v>
       </c>
       <c r="W478" s="115"/>
       <c r="X478" s="115"/>
@@ -33728,10 +33733,10 @@
     </row>
     <row r="479" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A479" s="139" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="B479" s="116" t="s">
-        <v>1923</v>
+        <v>1921</v>
       </c>
       <c r="D479" s="83">
         <v>41045</v>
@@ -33756,7 +33761,7 @@
       <c r="T479" s="177"/>
       <c r="U479" s="115"/>
       <c r="V479" s="115" t="s">
-        <v>1925</v>
+        <v>1923</v>
       </c>
       <c r="W479" s="115"/>
       <c r="X479" s="115"/>
@@ -33768,10 +33773,10 @@
     </row>
     <row r="480" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A480" s="139" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="B480" s="116" t="s">
-        <v>1927</v>
+        <v>1925</v>
       </c>
       <c r="D480" s="83">
         <v>41046</v>
@@ -33806,7 +33811,7 @@
       <c r="T480" s="177"/>
       <c r="U480" s="115"/>
       <c r="V480" s="115" t="s">
-        <v>1928</v>
+        <v>1926</v>
       </c>
       <c r="W480" s="115"/>
       <c r="X480" s="115"/>
@@ -33818,10 +33823,10 @@
     </row>
     <row r="481" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A481" s="139" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="B481" s="116" t="s">
-        <v>1930</v>
+        <v>1928</v>
       </c>
       <c r="D481" s="83">
         <v>41047</v>
@@ -33846,7 +33851,7 @@
       <c r="T481" s="177"/>
       <c r="U481" s="115"/>
       <c r="V481" s="115" t="s">
-        <v>1931</v>
+        <v>1929</v>
       </c>
       <c r="W481" s="115"/>
       <c r="X481" s="115"/>
@@ -33858,10 +33863,10 @@
     </row>
     <row r="482" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A482" s="139" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="B482" s="116" t="s">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="D482" s="83">
         <v>41048</v>
@@ -33892,7 +33897,7 @@
       <c r="T482" s="177"/>
       <c r="U482" s="115"/>
       <c r="V482" s="115" t="s">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="W482" s="115"/>
       <c r="X482" s="115"/>
@@ -33904,10 +33909,10 @@
     </row>
     <row r="483" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A483" s="139" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="B483" s="116" t="s">
-        <v>1960</v>
+        <v>1958</v>
       </c>
       <c r="D483" s="83">
         <v>41049</v>
@@ -33938,7 +33943,7 @@
       <c r="T483" s="177"/>
       <c r="U483" s="115"/>
       <c r="V483" s="115" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="W483" s="115"/>
       <c r="X483" s="115"/>
@@ -33950,10 +33955,10 @@
     </row>
     <row r="484" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A484" s="139" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="B484" s="116" t="s">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="D484" s="83">
         <v>41050</v>
@@ -33984,7 +33989,7 @@
       <c r="T484" s="177"/>
       <c r="U484" s="115"/>
       <c r="V484" s="115" t="s">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="W484" s="115"/>
       <c r="X484" s="115"/>
@@ -33996,10 +34001,10 @@
     </row>
     <row r="485" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A485" s="139" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="B485" s="116" t="s">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="D485" s="83">
         <v>41051</v>
@@ -34030,7 +34035,7 @@
       <c r="T485" s="177"/>
       <c r="U485" s="115"/>
       <c r="V485" s="115" t="s">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="W485" s="115"/>
       <c r="X485" s="115"/>
@@ -34042,10 +34047,10 @@
     </row>
     <row r="486" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A486" s="139" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="B486" s="116" t="s">
-        <v>2053</v>
+        <v>2051</v>
       </c>
       <c r="D486" s="83">
         <v>41052</v>
@@ -34080,7 +34085,7 @@
       <c r="T486" s="177"/>
       <c r="U486" s="115"/>
       <c r="V486" s="115" t="s">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="W486" s="115"/>
       <c r="X486" s="115"/>
@@ -34092,10 +34097,10 @@
     </row>
     <row r="487" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A487" s="139" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="B487" s="116" t="s">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="D487" s="83">
         <v>41053</v>
@@ -34130,7 +34135,7 @@
       <c r="T487" s="177"/>
       <c r="U487" s="115"/>
       <c r="V487" s="115" t="s">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="W487" s="115"/>
       <c r="X487" s="115"/>
@@ -34142,10 +34147,10 @@
     </row>
     <row r="488" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A488" s="139" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="B488" s="116" t="s">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="D488" s="83">
         <v>41054</v>
@@ -34170,7 +34175,7 @@
       <c r="T488" s="177"/>
       <c r="U488" s="115"/>
       <c r="V488" s="115" t="s">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="W488" s="115"/>
       <c r="X488" s="115"/>
@@ -34182,10 +34187,10 @@
     </row>
     <row r="489" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A489" s="139" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="B489" s="116" t="s">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="D489" s="83">
         <v>41055</v>
@@ -34210,7 +34215,7 @@
       <c r="T489" s="177"/>
       <c r="U489" s="115"/>
       <c r="V489" s="115" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="W489" s="115"/>
       <c r="X489" s="115"/>
@@ -34228,10 +34233,10 @@
     </row>
     <row r="490" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A490" s="139" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="B490" s="116" t="s">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="D490" s="83">
         <v>41056</v>
@@ -34256,7 +34261,7 @@
       <c r="T490" s="177"/>
       <c r="U490" s="115"/>
       <c r="V490" s="115" t="s">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="W490" s="115"/>
       <c r="X490" s="115"/>
@@ -34274,10 +34279,10 @@
     </row>
     <row r="491" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A491" s="139" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="B491" s="116" t="s">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="D491" s="83">
         <v>41057</v>
@@ -34302,7 +34307,7 @@
       <c r="T491" s="177"/>
       <c r="U491" s="115"/>
       <c r="V491" s="115" t="s">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="W491" s="115"/>
       <c r="X491" s="115"/>
@@ -34314,10 +34319,10 @@
     </row>
     <row r="492" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A492" s="139" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="B492" s="116" t="s">
-        <v>2027</v>
+        <v>2025</v>
       </c>
       <c r="D492" s="83">
         <v>41058</v>
@@ -34352,7 +34357,7 @@
       <c r="T492" s="177"/>
       <c r="U492" s="115"/>
       <c r="V492" s="115" t="s">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="W492" s="115"/>
       <c r="X492" s="115"/>
@@ -34525,7 +34530,7 @@
     <row r="497" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A497" s="139"/>
       <c r="B497" s="116" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="C497" s="117"/>
       <c r="D497" s="83">
@@ -34553,7 +34558,7 @@
       <c r="V497" s="115"/>
       <c r="W497" s="115"/>
       <c r="X497" s="115" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="Y497" s="115"/>
       <c r="Z497" s="115"/>
@@ -34924,7 +34929,7 @@
         <v>885</v>
       </c>
       <c r="B506" s="116" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="C506" s="117"/>
       <c r="D506" s="83">
@@ -34950,7 +34955,7 @@
       <c r="T506" s="137"/>
       <c r="U506" s="115"/>
       <c r="V506" s="115" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
       <c r="W506" s="144"/>
       <c r="X506" s="115"/>
@@ -34991,7 +34996,7 @@
       <c r="T507" s="137"/>
       <c r="U507" s="115"/>
       <c r="V507" s="115" t="s">
-        <v>1818</v>
+        <v>1816</v>
       </c>
       <c r="W507" s="83"/>
       <c r="X507" s="115"/>
@@ -35032,7 +35037,7 @@
       <c r="T508" s="137"/>
       <c r="U508" s="115"/>
       <c r="V508" s="115" t="s">
-        <v>1916</v>
+        <v>1914</v>
       </c>
       <c r="W508" s="83"/>
       <c r="X508" s="115"/>
@@ -35398,7 +35403,7 @@
       <c r="T516" s="137"/>
       <c r="U516" s="115"/>
       <c r="V516" s="115" t="s">
-        <v>2051</v>
+        <v>2049</v>
       </c>
       <c r="W516" s="83"/>
       <c r="X516" s="115"/>
@@ -35580,7 +35585,7 @@
       <c r="T520" s="137"/>
       <c r="U520" s="115"/>
       <c r="V520" s="115" t="s">
-        <v>2052</v>
+        <v>2050</v>
       </c>
       <c r="W520" s="83"/>
       <c r="X520" s="115"/>
@@ -35930,9 +35935,9 @@
       <c r="T528" s="137"/>
       <c r="U528" s="115"/>
       <c r="V528" s="115"/>
-      <c r="W528" s="83"/>
+      <c r="W528" s="115"/>
       <c r="X528" s="115" t="s">
-        <v>1817</v>
+        <v>2054</v>
       </c>
       <c r="Y528" s="115"/>
       <c r="Z528" s="115"/>
@@ -35983,10 +35988,10 @@
     </row>
     <row r="530" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A530" s="1" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B530" s="116" t="s">
         <v>1748</v>
-      </c>
-      <c r="B530" s="116" t="s">
-        <v>1749</v>
       </c>
       <c r="C530" s="117"/>
       <c r="D530" s="83">
@@ -36012,28 +36017,28 @@
       <c r="T530" s="137"/>
       <c r="U530" s="115"/>
       <c r="V530" s="115" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="W530" s="115"/>
       <c r="X530" s="115"/>
       <c r="Y530" s="115"/>
       <c r="Z530" s="83" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="AA530" s="83" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="AB530" s="83" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="AC530" s="142"/>
     </row>
     <row r="531" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A531" s="1" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
       <c r="B531" s="116" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="C531" s="117"/>
       <c r="D531" s="83">
@@ -36059,28 +36064,28 @@
       <c r="T531" s="137"/>
       <c r="U531" s="115"/>
       <c r="V531" s="115" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
       <c r="W531" s="115"/>
       <c r="X531" s="115"/>
       <c r="Y531" s="115"/>
       <c r="Z531" s="115" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="AA531" s="115" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="AB531" s="115" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="AC531" s="142"/>
     </row>
     <row r="532" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A532" s="1" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
       <c r="B532" s="116" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="C532" s="117"/>
       <c r="D532" s="83">
@@ -36106,7 +36111,7 @@
       <c r="T532" s="137"/>
       <c r="U532" s="115"/>
       <c r="V532" s="115" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="W532" s="115"/>
       <c r="X532" s="115"/>
@@ -36124,10 +36129,10 @@
     </row>
     <row r="533" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A533" s="1" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
       <c r="B533" s="116" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="C533" s="117"/>
       <c r="D533" s="83">
@@ -36157,7 +36162,7 @@
       <c r="V533" s="115"/>
       <c r="W533" s="115"/>
       <c r="X533" s="115" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
       <c r="Y533" s="115"/>
       <c r="Z533" s="115"/>
@@ -36167,10 +36172,10 @@
     </row>
     <row r="534" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A534" s="1" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
       <c r="B534" s="116" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="C534" s="117"/>
       <c r="D534" s="83">
@@ -36200,7 +36205,7 @@
       <c r="V534" s="115"/>
       <c r="W534" s="115"/>
       <c r="X534" s="115" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="Y534" s="115"/>
       <c r="Z534" s="115"/>
@@ -36210,10 +36215,10 @@
     </row>
     <row r="535" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A535" s="1" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
       <c r="B535" s="116" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="C535" s="117"/>
       <c r="D535" s="83">
@@ -36243,7 +36248,7 @@
       <c r="V535" s="115"/>
       <c r="W535" s="115"/>
       <c r="X535" s="115" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="Y535" s="115"/>
       <c r="Z535" s="115"/>
@@ -36253,10 +36258,10 @@
     </row>
     <row r="536" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A536" s="1" t="s">
-        <v>1819</v>
+        <v>1817</v>
       </c>
       <c r="B536" s="116" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="C536" s="117"/>
       <c r="D536" s="83">
@@ -36282,7 +36287,7 @@
       <c r="T536" s="137"/>
       <c r="U536" s="115"/>
       <c r="V536" s="115" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="W536" s="83"/>
       <c r="X536" s="115"/>
@@ -36294,10 +36299,10 @@
     </row>
     <row r="537" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A537" s="1" t="s">
+        <v>1982</v>
+      </c>
+      <c r="B537" s="116" t="s">
         <v>1984</v>
-      </c>
-      <c r="B537" s="116" t="s">
-        <v>1986</v>
       </c>
       <c r="C537" s="117"/>
       <c r="D537" s="83">
@@ -36332,31 +36337,31 @@
       <c r="S537" s="137"/>
       <c r="T537" s="177"/>
       <c r="U537" s="115" t="s">
-        <v>1990</v>
+        <v>1988</v>
       </c>
       <c r="V537" s="115"/>
       <c r="W537" s="83"/>
       <c r="X537" s="115" t="s">
-        <v>1992</v>
+        <v>1990</v>
       </c>
       <c r="Y537" s="115"/>
       <c r="Z537" s="115" t="s">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="AA537" s="115" t="s">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="AB537" s="115" t="s">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="AC537" s="142"/>
     </row>
     <row r="538" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A538" s="1" t="s">
-        <v>1984</v>
+        <v>1982</v>
       </c>
       <c r="B538" s="116" t="s">
-        <v>1985</v>
+        <v>1983</v>
       </c>
       <c r="C538" s="117"/>
       <c r="D538" s="83">
@@ -36391,12 +36396,12 @@
       <c r="S538" s="137"/>
       <c r="T538" s="177"/>
       <c r="U538" s="115" t="s">
-        <v>1989</v>
+        <v>1987</v>
       </c>
       <c r="V538" s="115"/>
       <c r="W538" s="83"/>
       <c r="X538" s="115" t="s">
-        <v>1993</v>
+        <v>1991</v>
       </c>
       <c r="Y538" s="115"/>
       <c r="Z538" s="115" t="s">
@@ -36412,10 +36417,10 @@
     </row>
     <row r="539" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A539" s="1" t="s">
-        <v>1984</v>
+        <v>1982</v>
       </c>
       <c r="B539" s="116" t="s">
-        <v>1987</v>
+        <v>1985</v>
       </c>
       <c r="C539" s="117"/>
       <c r="D539" s="83">
@@ -36448,10 +36453,10 @@
       <c r="S539" s="137"/>
       <c r="T539" s="177"/>
       <c r="U539" s="115" t="s">
-        <v>1991</v>
+        <v>1989</v>
       </c>
       <c r="V539" s="83" t="s">
-        <v>1988</v>
+        <v>1986</v>
       </c>
       <c r="W539" s="83"/>
       <c r="X539" s="115"/>
@@ -36469,10 +36474,10 @@
     </row>
     <row r="540" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A540" s="1" t="s">
-        <v>1984</v>
+        <v>1982</v>
       </c>
       <c r="B540" s="116" t="s">
-        <v>1994</v>
+        <v>1992</v>
       </c>
       <c r="C540" s="117"/>
       <c r="D540" s="83">
@@ -36508,7 +36513,7 @@
       <c r="T540" s="177"/>
       <c r="U540" s="115"/>
       <c r="V540" s="115" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="W540" s="83"/>
       <c r="X540" s="115"/>
@@ -36520,10 +36525,10 @@
     </row>
     <row r="541" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A541" s="1" t="s">
-        <v>1984</v>
+        <v>1982</v>
       </c>
       <c r="B541" s="116" t="s">
-        <v>1995</v>
+        <v>1993</v>
       </c>
       <c r="C541" s="117"/>
       <c r="D541" s="83">
@@ -36557,7 +36562,7 @@
       <c r="T541" s="177"/>
       <c r="U541" s="115"/>
       <c r="V541" s="115" t="s">
-        <v>1996</v>
+        <v>1994</v>
       </c>
       <c r="W541" s="83"/>
       <c r="X541" s="115"/>
@@ -36569,10 +36574,10 @@
     </row>
     <row r="542" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A542" s="1" t="s">
-        <v>1984</v>
+        <v>1982</v>
       </c>
       <c r="B542" s="116" t="s">
-        <v>1997</v>
+        <v>1995</v>
       </c>
       <c r="C542" s="117"/>
       <c r="D542" s="83">
@@ -36608,7 +36613,7 @@
       <c r="T542" s="177"/>
       <c r="U542" s="115"/>
       <c r="V542" s="115" t="s">
-        <v>1998</v>
+        <v>1996</v>
       </c>
       <c r="W542" s="83"/>
       <c r="X542" s="115"/>
@@ -36620,10 +36625,10 @@
     </row>
     <row r="543" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A543" s="1" t="s">
-        <v>1984</v>
+        <v>1982</v>
       </c>
       <c r="B543" s="116" t="s">
-        <v>1999</v>
+        <v>1997</v>
       </c>
       <c r="C543" s="117"/>
       <c r="D543" s="83">
@@ -36651,7 +36656,7 @@
       <c r="T543" s="177"/>
       <c r="U543" s="115"/>
       <c r="V543" s="115" t="s">
-        <v>2000</v>
+        <v>1998</v>
       </c>
       <c r="W543" s="83"/>
       <c r="X543" s="115"/>
@@ -37195,7 +37200,7 @@
       <c r="T556" s="139"/>
       <c r="U556" s="83"/>
       <c r="V556" s="83" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="W556" s="83"/>
       <c r="X556" s="83"/>
@@ -37235,7 +37240,7 @@
       <c r="T557" s="139"/>
       <c r="U557" s="83"/>
       <c r="V557" s="83" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
       <c r="W557" s="83"/>
       <c r="X557" s="83"/>
@@ -37313,10 +37318,10 @@
       <c r="T559" s="182"/>
       <c r="U559" s="83"/>
       <c r="V559" s="115" t="s">
-        <v>2040</v>
+        <v>2038</v>
       </c>
       <c r="W559" s="115" t="s">
-        <v>2039</v>
+        <v>2037</v>
       </c>
       <c r="X559" s="83"/>
       <c r="Y559" s="83"/>
@@ -37353,10 +37358,10 @@
       <c r="T560" s="182"/>
       <c r="U560" s="83"/>
       <c r="V560" s="115" t="s">
+        <v>2039</v>
+      </c>
+      <c r="W560" s="115" t="s">
         <v>2041</v>
-      </c>
-      <c r="W560" s="115" t="s">
-        <v>2043</v>
       </c>
       <c r="X560" s="83"/>
       <c r="Y560" s="83"/>
@@ -37393,10 +37398,10 @@
       <c r="T561" s="182"/>
       <c r="U561" s="83"/>
       <c r="V561" s="115" t="s">
+        <v>2040</v>
+      </c>
+      <c r="W561" s="115" t="s">
         <v>2042</v>
-      </c>
-      <c r="W561" s="115" t="s">
-        <v>2044</v>
       </c>
       <c r="X561" s="83"/>
       <c r="Y561" s="83"/>
@@ -37408,7 +37413,7 @@
     <row r="562" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A562" s="1"/>
       <c r="B562" s="156" t="s">
-        <v>2031</v>
+        <v>2029</v>
       </c>
       <c r="D562" s="83">
         <v>70011</v>
@@ -37435,7 +37440,7 @@
       <c r="V562" s="83"/>
       <c r="W562" s="83"/>
       <c r="X562" s="83" t="s">
-        <v>2037</v>
+        <v>2035</v>
       </c>
       <c r="Y562" s="83"/>
       <c r="Z562" s="83"/>
@@ -37446,7 +37451,7 @@
     <row r="563" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A563" s="1"/>
       <c r="B563" s="156" t="s">
-        <v>2032</v>
+        <v>2030</v>
       </c>
       <c r="D563" s="83">
         <v>70012</v>
@@ -37475,7 +37480,7 @@
       <c r="T563" s="182"/>
       <c r="U563" s="83"/>
       <c r="V563" s="83" t="s">
-        <v>2035</v>
+        <v>2033</v>
       </c>
       <c r="W563" s="83"/>
       <c r="X563" s="83"/>
@@ -37494,7 +37499,7 @@
     <row r="564" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A564" s="1"/>
       <c r="B564" s="156" t="s">
-        <v>2036</v>
+        <v>2034</v>
       </c>
       <c r="D564" s="83">
         <v>70013</v>
@@ -37519,7 +37524,7 @@
       <c r="T564" s="182"/>
       <c r="U564" s="83"/>
       <c r="V564" s="115" t="s">
-        <v>2038</v>
+        <v>2036</v>
       </c>
       <c r="W564" s="83"/>
       <c r="X564" s="83"/>
@@ -37712,7 +37717,7 @@
     <row r="568" spans="1:29" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A568" s="1"/>
       <c r="B568" s="156" t="s">
-        <v>2045</v>
+        <v>2043</v>
       </c>
       <c r="D568" s="83">
         <v>70017</v>
@@ -37737,7 +37742,7 @@
       <c r="T568" s="182"/>
       <c r="U568" s="83"/>
       <c r="V568" s="83" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="W568" s="115"/>
       <c r="X568" s="83"/>
@@ -39209,350 +39214,350 @@
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="B366:C366">
-    <cfRule type="duplicateValues" dxfId="165" priority="325"/>
+    <cfRule type="duplicateValues" dxfId="191" priority="325"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D7">
-    <cfRule type="duplicateValues" dxfId="164" priority="16563"/>
+    <cfRule type="duplicateValues" dxfId="190" priority="16563"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D21">
-    <cfRule type="duplicateValues" dxfId="163" priority="251"/>
-    <cfRule type="duplicateValues" dxfId="162" priority="252"/>
+    <cfRule type="duplicateValues" dxfId="189" priority="251"/>
+    <cfRule type="duplicateValues" dxfId="188" priority="252"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D29:D30">
-    <cfRule type="duplicateValues" dxfId="161" priority="207"/>
-    <cfRule type="duplicateValues" dxfId="160" priority="208"/>
+    <cfRule type="duplicateValues" dxfId="187" priority="207"/>
+    <cfRule type="duplicateValues" dxfId="186" priority="208"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D47:D83">
-    <cfRule type="duplicateValues" dxfId="159" priority="16728"/>
-    <cfRule type="duplicateValues" dxfId="158" priority="16729"/>
+    <cfRule type="duplicateValues" dxfId="185" priority="16728"/>
+    <cfRule type="duplicateValues" dxfId="184" priority="16729"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D84">
-    <cfRule type="duplicateValues" dxfId="157" priority="484"/>
-    <cfRule type="duplicateValues" dxfId="156" priority="487"/>
-    <cfRule type="duplicateValues" dxfId="155" priority="491"/>
+    <cfRule type="duplicateValues" dxfId="183" priority="484"/>
+    <cfRule type="duplicateValues" dxfId="182" priority="487"/>
+    <cfRule type="duplicateValues" dxfId="181" priority="491"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D85">
-    <cfRule type="duplicateValues" dxfId="154" priority="474"/>
-    <cfRule type="duplicateValues" dxfId="153" priority="477"/>
-    <cfRule type="duplicateValues" dxfId="152" priority="481"/>
+    <cfRule type="duplicateValues" dxfId="180" priority="474"/>
+    <cfRule type="duplicateValues" dxfId="179" priority="477"/>
+    <cfRule type="duplicateValues" dxfId="178" priority="481"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D86">
-    <cfRule type="duplicateValues" dxfId="151" priority="494"/>
-    <cfRule type="duplicateValues" dxfId="150" priority="497"/>
-    <cfRule type="duplicateValues" dxfId="149" priority="500"/>
+    <cfRule type="duplicateValues" dxfId="177" priority="494"/>
+    <cfRule type="duplicateValues" dxfId="176" priority="497"/>
+    <cfRule type="duplicateValues" dxfId="175" priority="500"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D87">
-    <cfRule type="duplicateValues" dxfId="148" priority="503"/>
-    <cfRule type="duplicateValues" dxfId="147" priority="506"/>
-    <cfRule type="duplicateValues" dxfId="146" priority="509"/>
+    <cfRule type="duplicateValues" dxfId="174" priority="503"/>
+    <cfRule type="duplicateValues" dxfId="173" priority="506"/>
+    <cfRule type="duplicateValues" dxfId="172" priority="509"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D88">
-    <cfRule type="duplicateValues" dxfId="145" priority="551"/>
+    <cfRule type="duplicateValues" dxfId="171" priority="551"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D88:D104">
-    <cfRule type="duplicateValues" dxfId="144" priority="16398"/>
-    <cfRule type="duplicateValues" dxfId="143" priority="16399"/>
-    <cfRule type="duplicateValues" dxfId="142" priority="16400"/>
+    <cfRule type="duplicateValues" dxfId="170" priority="16398"/>
+    <cfRule type="duplicateValues" dxfId="169" priority="16399"/>
+    <cfRule type="duplicateValues" dxfId="168" priority="16400"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D89 D91:D104">
-    <cfRule type="duplicateValues" dxfId="141" priority="552"/>
+    <cfRule type="duplicateValues" dxfId="167" priority="552"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D90:D104">
-    <cfRule type="duplicateValues" dxfId="140" priority="554"/>
+    <cfRule type="duplicateValues" dxfId="166" priority="554"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D105:D107">
-    <cfRule type="duplicateValues" dxfId="139" priority="528"/>
-    <cfRule type="duplicateValues" dxfId="138" priority="531"/>
-    <cfRule type="duplicateValues" dxfId="137" priority="535"/>
+    <cfRule type="duplicateValues" dxfId="165" priority="528"/>
+    <cfRule type="duplicateValues" dxfId="164" priority="531"/>
+    <cfRule type="duplicateValues" dxfId="163" priority="535"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D108">
-    <cfRule type="duplicateValues" dxfId="136" priority="16014"/>
-    <cfRule type="duplicateValues" dxfId="135" priority="16015"/>
-    <cfRule type="duplicateValues" dxfId="134" priority="16016"/>
-    <cfRule type="duplicateValues" dxfId="133" priority="16018"/>
-    <cfRule type="duplicateValues" dxfId="132" priority="16020"/>
-    <cfRule type="duplicateValues" dxfId="131" priority="16025"/>
-    <cfRule type="duplicateValues" dxfId="130" priority="16027"/>
+    <cfRule type="duplicateValues" dxfId="162" priority="16014"/>
+    <cfRule type="duplicateValues" dxfId="161" priority="16015"/>
+    <cfRule type="duplicateValues" dxfId="160" priority="16016"/>
+    <cfRule type="duplicateValues" dxfId="159" priority="16018"/>
+    <cfRule type="duplicateValues" dxfId="158" priority="16020"/>
+    <cfRule type="duplicateValues" dxfId="157" priority="16025"/>
+    <cfRule type="duplicateValues" dxfId="156" priority="16027"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D162">
-    <cfRule type="duplicateValues" dxfId="129" priority="88"/>
-    <cfRule type="duplicateValues" dxfId="128" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="155" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="154" priority="89"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D169 D163 D165 D171 D173 D175 D167 D109:D161">
-    <cfRule type="duplicateValues" dxfId="127" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="153" priority="118"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D169 E142:R143 D163 D165 D171 D173 D175 D167 D109:D161">
-    <cfRule type="duplicateValues" dxfId="126" priority="119"/>
+    <cfRule type="duplicateValues" dxfId="152" priority="119"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D170 D164 D166 D172 D174 D176:D178 D216 D168 D218 D220:D221 D223:D224 D230 D180:D185 D226:D228 D187:D214">
-    <cfRule type="duplicateValues" dxfId="125" priority="120"/>
-    <cfRule type="duplicateValues" dxfId="124" priority="121"/>
+    <cfRule type="duplicateValues" dxfId="151" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="150" priority="121"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D179">
-    <cfRule type="duplicateValues" dxfId="123" priority="113"/>
-    <cfRule type="duplicateValues" dxfId="122" priority="114"/>
+    <cfRule type="duplicateValues" dxfId="149" priority="113"/>
+    <cfRule type="duplicateValues" dxfId="148" priority="114"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D186">
-    <cfRule type="duplicateValues" dxfId="121" priority="107"/>
-    <cfRule type="duplicateValues" dxfId="120" priority="108"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="146" priority="108"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D215 D217 D219 D222 D225 D229">
-    <cfRule type="duplicateValues" dxfId="119" priority="115"/>
-    <cfRule type="duplicateValues" dxfId="118" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="145" priority="115"/>
+    <cfRule type="duplicateValues" dxfId="144" priority="116"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D238:D239">
-    <cfRule type="duplicateValues" dxfId="117" priority="111"/>
-    <cfRule type="duplicateValues" dxfId="116" priority="112"/>
+    <cfRule type="duplicateValues" dxfId="143" priority="111"/>
+    <cfRule type="duplicateValues" dxfId="142" priority="112"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D361">
-    <cfRule type="duplicateValues" dxfId="115" priority="149"/>
-    <cfRule type="duplicateValues" dxfId="114" priority="152"/>
+    <cfRule type="duplicateValues" dxfId="141" priority="149"/>
+    <cfRule type="duplicateValues" dxfId="140" priority="152"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D362:D363">
-    <cfRule type="duplicateValues" dxfId="113" priority="328"/>
+    <cfRule type="duplicateValues" dxfId="139" priority="328"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D362:D374">
-    <cfRule type="duplicateValues" dxfId="112" priority="16333"/>
-    <cfRule type="duplicateValues" dxfId="111" priority="16334"/>
+    <cfRule type="duplicateValues" dxfId="138" priority="16333"/>
+    <cfRule type="duplicateValues" dxfId="137" priority="16334"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D364">
-    <cfRule type="duplicateValues" dxfId="110" priority="327"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="327"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D365">
-    <cfRule type="duplicateValues" dxfId="109" priority="326"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="326"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D366:D374">
-    <cfRule type="duplicateValues" dxfId="108" priority="16335"/>
-    <cfRule type="duplicateValues" dxfId="107" priority="16336"/>
+    <cfRule type="duplicateValues" dxfId="134" priority="16335"/>
+    <cfRule type="duplicateValues" dxfId="133" priority="16336"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D375:D382">
-    <cfRule type="duplicateValues" dxfId="106" priority="124"/>
-    <cfRule type="duplicateValues" dxfId="105" priority="125"/>
-    <cfRule type="duplicateValues" dxfId="104" priority="126"/>
-    <cfRule type="duplicateValues" dxfId="103" priority="127"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="124"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="125"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="126"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="127"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D383">
-    <cfRule type="duplicateValues" dxfId="102" priority="59"/>
-    <cfRule type="duplicateValues" dxfId="101" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="127" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D384">
-    <cfRule type="duplicateValues" dxfId="100" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="99" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="126" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="125" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D385">
-    <cfRule type="duplicateValues" dxfId="98" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="97" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D386">
-    <cfRule type="duplicateValues" dxfId="96" priority="273"/>
-    <cfRule type="duplicateValues" dxfId="95" priority="274"/>
-    <cfRule type="duplicateValues" dxfId="94" priority="275"/>
-    <cfRule type="duplicateValues" dxfId="93" priority="276"/>
+    <cfRule type="duplicateValues" dxfId="122" priority="273"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="274"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="275"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="276"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D387">
-    <cfRule type="duplicateValues" dxfId="92" priority="263"/>
-    <cfRule type="duplicateValues" dxfId="91" priority="264"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="263"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="264"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D388:D389">
-    <cfRule type="duplicateValues" dxfId="90" priority="16338"/>
-    <cfRule type="duplicateValues" dxfId="89" priority="16339"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="16338"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="16339"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D390">
-    <cfRule type="duplicateValues" dxfId="88" priority="130"/>
-    <cfRule type="duplicateValues" dxfId="87" priority="131"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="130"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="131"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D391">
-    <cfRule type="duplicateValues" dxfId="86" priority="265"/>
-    <cfRule type="duplicateValues" dxfId="85" priority="266"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="265"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="266"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D392">
-    <cfRule type="duplicateValues" dxfId="84" priority="267"/>
-    <cfRule type="duplicateValues" dxfId="83" priority="268"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="267"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="268"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D393">
-    <cfRule type="duplicateValues" dxfId="82" priority="259"/>
-    <cfRule type="duplicateValues" dxfId="81" priority="260"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="259"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="260"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D394">
-    <cfRule type="duplicateValues" dxfId="80" priority="249"/>
-    <cfRule type="duplicateValues" dxfId="79" priority="250"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="249"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="250"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D395:D396">
-    <cfRule type="duplicateValues" dxfId="78" priority="233"/>
-    <cfRule type="duplicateValues" dxfId="77" priority="234"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="233"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="234"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D397">
-    <cfRule type="duplicateValues" dxfId="76" priority="219"/>
-    <cfRule type="duplicateValues" dxfId="75" priority="220"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="219"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="220"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D398">
-    <cfRule type="duplicateValues" dxfId="74" priority="221"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="222"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="221"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="222"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D399">
-    <cfRule type="duplicateValues" dxfId="72" priority="217"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="218"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="217"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="218"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D400">
-    <cfRule type="duplicateValues" dxfId="70" priority="215"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="216"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="215"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="216"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D401">
-    <cfRule type="duplicateValues" dxfId="68" priority="185"/>
-    <cfRule type="duplicateValues" dxfId="67" priority="186"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="185"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="186"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D402">
-    <cfRule type="duplicateValues" dxfId="66" priority="183"/>
-    <cfRule type="duplicateValues" dxfId="65" priority="184"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="183"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="184"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D403 D405">
-    <cfRule type="duplicateValues" dxfId="64" priority="134"/>
-    <cfRule type="duplicateValues" dxfId="63" priority="135"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="134"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="135"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D404">
-    <cfRule type="duplicateValues" dxfId="62" priority="90"/>
-    <cfRule type="duplicateValues" dxfId="61" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="91"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D406">
-    <cfRule type="duplicateValues" dxfId="60" priority="105"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="106"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="105"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="106"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D407:D434">
-    <cfRule type="duplicateValues" dxfId="58" priority="16039"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="16042"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="16039"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="16042"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D442:D450 D452 D455">
-    <cfRule type="duplicateValues" dxfId="56" priority="16629"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="16632"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="16629"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="16632"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D451 D453:D454 D456:D459">
-    <cfRule type="duplicateValues" dxfId="54" priority="16613"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="16616"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="16613"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="16616"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D461">
-    <cfRule type="duplicateValues" dxfId="52" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D493:D497 D435:D441">
-    <cfRule type="duplicateValues" dxfId="50" priority="16533"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="16536"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="16533"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="16536"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D498:D516">
-    <cfRule type="duplicateValues" dxfId="48" priority="16483"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="16486"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="16483"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="16486"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D517:D521 D523:D528 D530:D531 D533:D534 D536:D537 D539:D540 D542:D543">
-    <cfRule type="duplicateValues" dxfId="46" priority="16545"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="16548"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="16545"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="16548"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D522">
-    <cfRule type="duplicateValues" dxfId="44" priority="71"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="74"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D529 D532 D535 D538 D541">
-    <cfRule type="duplicateValues" dxfId="42" priority="67"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D569:D601">
-    <cfRule type="duplicateValues" dxfId="40" priority="82"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="83"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="84"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="85"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="86"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D602:D1048576 D8:D20 D1:D4 D22:D28 D31:D46 D6 D544:D568">
-    <cfRule type="duplicateValues" dxfId="35" priority="15257"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="15999"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="15257"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="15999"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D602:D1048576 D544:D568">
-    <cfRule type="duplicateValues" dxfId="33" priority="15176"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="15313"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="16003"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="15176"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="15313"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="16003"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D7:H7 L7:N7">
-    <cfRule type="duplicateValues" dxfId="30" priority="16600"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="16600"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E136:O136">
-    <cfRule type="duplicateValues" dxfId="29" priority="117"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="117"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L49:N49">
-    <cfRule type="duplicateValues" dxfId="28" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L162:N162">
-    <cfRule type="duplicateValues" dxfId="27" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="87"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L250:N250">
-    <cfRule type="duplicateValues" dxfId="26" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L289:N289">
-    <cfRule type="duplicateValues" dxfId="25" priority="110"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="110"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L321:N321">
-    <cfRule type="duplicateValues" dxfId="24" priority="109"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="109"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L432:N432">
-    <cfRule type="duplicateValues" dxfId="23" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L571:N571">
-    <cfRule type="duplicateValues" dxfId="22" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="80"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L574:N574">
-    <cfRule type="duplicateValues" dxfId="21" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="81"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="S366 S362 S364">
-    <cfRule type="duplicateValues" dxfId="20" priority="329"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="329"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="S367:S368 S363 S365">
-    <cfRule type="duplicateValues" dxfId="19" priority="16337"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="16337"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D338 D341">
-    <cfRule type="duplicateValues" dxfId="18" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D338 D341">
-    <cfRule type="duplicateValues" dxfId="17" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D231:D237 D339:D340 D240:D337 D342:D353 D355 D359:D360 D357">
-    <cfRule type="duplicateValues" dxfId="16" priority="16732"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="16733"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="16732"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="16733"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D354 D356 D358">
-    <cfRule type="duplicateValues" dxfId="14" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5">
-    <cfRule type="duplicateValues" dxfId="12" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5">
-    <cfRule type="duplicateValues" dxfId="11" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5">
-    <cfRule type="duplicateValues" dxfId="10" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5">
-    <cfRule type="duplicateValues" dxfId="9" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5">
-    <cfRule type="duplicateValues" dxfId="8" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5">
-    <cfRule type="duplicateValues" dxfId="7" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5">
-    <cfRule type="duplicateValues" dxfId="6" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5">
-    <cfRule type="duplicateValues" dxfId="5" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5">
-    <cfRule type="duplicateValues" dxfId="4" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D485 D487 D489 D491">
-    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D460 D462:D484 D486 D488 D490 D492">
-    <cfRule type="duplicateValues" dxfId="1" priority="16734"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="16735"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="16734"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="16735"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -39725,7 +39730,7 @@
         <v>1041</v>
       </c>
       <c r="C15" s="40" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="D15" s="41" t="s">
         <v>1042</v>
@@ -55567,7 +55572,7 @@
         <v>1601</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1877</v>
+        <v>1875</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>1602</v>
@@ -55611,7 +55616,7 @@
         <v>1609</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>1610</v>
@@ -55655,51 +55660,51 @@
         <v>1619</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>2055</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>1620</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>1621</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="27" x14ac:dyDescent="0.15">
       <c r="A18" s="4" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>1621</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>1622</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>1623</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A19" s="1" t="s">
+        <v>1623</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>1745</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>1624</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>1746</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>1625</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A20" s="1" t="s">
+        <v>1625</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>1770</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>1626</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>1771</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>1627</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
+        <v>1627</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>1628</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>1629</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>1589</v>
@@ -55707,21 +55712,21 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A22" s="1" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>1589</v>
@@ -55729,46 +55734,46 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A24" s="1" t="s">
+        <v>1631</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>1632</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="C24" s="1" t="s">
         <v>1633</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>1634</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A25" s="1" t="s">
+        <v>1634</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>1635</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>1636</v>
-      </c>
       <c r="C25" s="1" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A26" s="1" t="s">
+        <v>1636</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>2032</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>1637</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>2034</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>1638</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A27" s="1" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>2033</v>
+        <v>2031</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
     </row>
   </sheetData>
